--- a/AIML304 ML/500 Question bank/Machine Learning Question Bank.xlsx
+++ b/AIML304 ML/500 Question bank/Machine Learning Question Bank.xlsx
@@ -1,14 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\B.Tech CSE with AI &amp; ML\Semester 3\Machine-Learning\AIML304 ML\500 Question bank\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE07807-3E4E-4E5B-9724-EB9CCA84DD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="495" windowWidth="23655" windowHeight="9405"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ml qb" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ml qb'!$G$1:$G$1000</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -2110,8 +2119,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2152,25 +2161,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2371,12 +2385,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="66.85546875" customWidth="1"/>
     <col min="3" max="3" width="25.85546875" customWidth="1"/>
@@ -2385,7 +2399,7 @@
     <col min="6" max="6" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2411,7 +2425,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2437,7 +2451,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2463,7 +2477,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2489,7 +2503,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2515,7 +2529,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2541,7 +2555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2567,7 +2581,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2593,7 +2607,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2619,7 +2633,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2645,7 +2659,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2671,7 +2685,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2697,7 +2711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2723,7 +2737,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2749,7 +2763,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2775,7 +2789,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2801,7 +2815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2827,7 +2841,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2853,7 +2867,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -2879,7 +2893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2905,7 +2919,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2931,7 +2945,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -2957,7 +2971,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -2983,7 +2997,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3009,7 +3023,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3035,7 +3049,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3061,7 +3075,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3087,7 +3101,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3113,7 +3127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3139,7 +3153,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3165,7 +3179,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3191,7 +3205,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3217,7 +3231,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3243,7 +3257,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3269,7 +3283,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3295,7 +3309,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3321,7 +3335,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3347,7 +3361,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3373,7 +3387,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -3399,7 +3413,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3425,7 +3439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3451,7 +3465,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -3477,7 +3491,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -3503,7 +3517,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -3529,7 +3543,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3555,7 +3569,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -3581,7 +3595,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -3607,7 +3621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -3633,7 +3647,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -3659,7 +3673,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -3685,7 +3699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -3711,7 +3725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -3737,7 +3751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -3763,7 +3777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -3789,7 +3803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3815,7 +3829,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -3841,7 +3855,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3867,7 +3881,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -3893,7 +3907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -3919,7 +3933,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -3945,7 +3959,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -3971,7 +3985,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -3997,7 +4011,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -4023,7 +4037,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -4049,7 +4063,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -4075,7 +4089,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -4101,7 +4115,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -4127,7 +4141,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -4153,7 +4167,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -4179,7 +4193,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -4205,7 +4219,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -4231,7 +4245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -4257,7 +4271,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -4283,7 +4297,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -4309,7 +4323,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -4335,7 +4349,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -4361,7 +4375,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -4387,7 +4401,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -4413,7 +4427,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -4439,7 +4453,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -4465,7 +4479,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -4491,7 +4505,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -4517,7 +4531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -4543,7 +4557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -4569,7 +4583,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -4595,7 +4609,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -4621,7 +4635,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -4647,7 +4661,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -4673,7 +4687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -4699,7 +4713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -4725,7 +4739,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -4751,7 +4765,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -4777,7 +4791,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -4803,7 +4817,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -4829,7 +4843,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -4855,7 +4869,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -4881,7 +4895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -4907,7 +4921,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -4933,7 +4947,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -4959,7 +4973,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -4985,7 +4999,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -5011,7 +5025,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -5037,7 +5051,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -5063,7 +5077,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -5089,7 +5103,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -5115,7 +5129,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -5141,7 +5155,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -5167,7 +5181,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -5193,7 +5207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -5219,7 +5233,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -5245,7 +5259,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -5271,7 +5285,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -5297,7 +5311,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -5323,7 +5337,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -5349,7 +5363,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -5375,7 +5389,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -5401,7 +5415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -5427,7 +5441,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -5453,7 +5467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -5479,7 +5493,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -5505,7 +5519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -5531,7 +5545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -5557,7 +5571,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -5583,7 +5597,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -5609,7 +5623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -5635,7 +5649,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -5661,7 +5675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -5687,7 +5701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -5713,7 +5727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -5739,7 +5753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -5765,7 +5779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -5791,7 +5805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -5817,7 +5831,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -5843,7 +5857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -5869,7 +5883,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -5895,7 +5909,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -5921,7 +5935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -5947,7 +5961,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -5973,7 +5987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -5999,7 +6013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -6025,7 +6039,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -6051,7 +6065,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -6077,7 +6091,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -6103,7 +6117,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -6129,7 +6143,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -6155,7 +6169,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>145</v>
       </c>
@@ -6181,7 +6195,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -6207,7 +6221,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>147</v>
       </c>
@@ -6233,7 +6247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -6259,7 +6273,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -6285,7 +6299,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -6311,7 +6325,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -6337,7 +6351,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -6363,7 +6377,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -6389,7 +6403,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -6415,7 +6429,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -6441,7 +6455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -6467,7 +6481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -6493,7 +6507,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -6519,7 +6533,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -6545,7 +6559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -6571,7 +6585,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -6597,7 +6611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -6623,7 +6637,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -6649,7 +6663,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -6675,7 +6689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -6701,7 +6715,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -6727,7 +6741,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -6753,7 +6767,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -6779,7 +6793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -6805,7 +6819,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -6831,7 +6845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -6857,7 +6871,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -6883,7 +6897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -6909,7 +6923,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
         <v>174</v>
       </c>
@@ -6935,7 +6949,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
         <v>175</v>
       </c>
@@ -6961,7 +6975,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="3">
         <v>176</v>
       </c>
@@ -6987,7 +7001,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="3">
         <v>177</v>
       </c>
@@ -7013,7 +7027,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="3">
         <v>178</v>
       </c>
@@ -7039,7 +7053,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -7065,7 +7079,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="3">
         <v>180</v>
       </c>
@@ -7091,7 +7105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -7117,7 +7131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="3">
         <v>182</v>
       </c>
@@ -7143,7 +7157,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -7169,7 +7183,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -7195,7 +7209,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -7221,7 +7235,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="3">
         <v>186</v>
       </c>
@@ -7247,7 +7261,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -7273,7 +7287,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="3">
         <v>188</v>
       </c>
@@ -7299,7 +7313,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
         <v>189</v>
       </c>
@@ -7325,7 +7339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="3">
         <v>190</v>
       </c>
@@ -7351,7 +7365,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
         <v>191</v>
       </c>
@@ -7377,7 +7391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="3">
         <v>192</v>
       </c>
@@ -7403,7 +7417,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="3">
         <v>193</v>
       </c>
@@ -7429,7 +7443,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -7455,7 +7469,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -7481,7 +7495,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="3">
         <v>196</v>
       </c>
@@ -7507,7 +7521,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>197</v>
       </c>
@@ -7533,7 +7547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="3">
         <v>198</v>
       </c>
@@ -7559,7 +7573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="3">
         <v>199</v>
       </c>
@@ -7585,7 +7599,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="3">
         <v>200</v>
       </c>
@@ -7611,7 +7625,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="3">
         <v>201</v>
       </c>
@@ -7625,7 +7639,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="3">
         <v>202</v>
       </c>
@@ -7639,7 +7653,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="3">
         <v>203</v>
       </c>
@@ -7653,7 +7667,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="3">
         <v>204</v>
       </c>
@@ -7667,7 +7681,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="3">
         <v>205</v>
       </c>
@@ -7681,7 +7695,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="3">
         <v>206</v>
       </c>
@@ -7695,7 +7709,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="3">
         <v>207</v>
       </c>
@@ -7709,7 +7723,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="3">
         <v>208</v>
       </c>
@@ -7723,7 +7737,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="3">
         <v>209</v>
       </c>
@@ -7737,7 +7751,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="3">
         <v>210</v>
       </c>
@@ -7751,7 +7765,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="3">
         <v>211</v>
       </c>
@@ -7765,7 +7779,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="3">
         <v>212</v>
       </c>
@@ -7779,7 +7793,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="3">
         <v>213</v>
       </c>
@@ -7793,7 +7807,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="3">
         <v>214</v>
       </c>
@@ -7807,7 +7821,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="3">
         <v>215</v>
       </c>
@@ -7821,7 +7835,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="3">
         <v>216</v>
       </c>
@@ -7835,7 +7849,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="3">
         <v>217</v>
       </c>
@@ -7849,7 +7863,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="3">
         <v>218</v>
       </c>
@@ -7863,7 +7877,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="3">
         <v>219</v>
       </c>
@@ -7877,7 +7891,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="3">
         <v>220</v>
       </c>
@@ -7891,7 +7905,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="3">
         <v>221</v>
       </c>
@@ -7905,7 +7919,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="3">
         <v>222</v>
       </c>
@@ -7919,7 +7933,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="3">
         <v>223</v>
       </c>
@@ -7933,7 +7947,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="3">
         <v>224</v>
       </c>
@@ -7947,7 +7961,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="3">
         <v>225</v>
       </c>
@@ -7961,7 +7975,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="3">
         <v>226</v>
       </c>
@@ -7975,7 +7989,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
         <v>227</v>
       </c>
@@ -7989,7 +8003,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="3">
         <v>228</v>
       </c>
@@ -8003,7 +8017,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="3">
         <v>229</v>
       </c>
@@ -8017,7 +8031,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="3">
         <v>230</v>
       </c>
@@ -8031,7 +8045,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="3">
         <v>231</v>
       </c>
@@ -8045,7 +8059,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="3">
         <v>232</v>
       </c>
@@ -8059,7 +8073,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="3">
         <v>233</v>
       </c>
@@ -8073,7 +8087,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="3">
         <v>234</v>
       </c>
@@ -8087,7 +8101,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="3">
         <v>235</v>
       </c>
@@ -8101,7 +8115,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="3">
         <v>236</v>
       </c>
@@ -8115,7 +8129,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="3">
         <v>237</v>
       </c>
@@ -8129,7 +8143,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="3">
         <v>238</v>
       </c>
@@ -8143,7 +8157,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="3">
         <v>239</v>
       </c>
@@ -8157,7 +8171,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="3">
         <v>240</v>
       </c>
@@ -8171,7 +8185,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="3">
         <v>241</v>
       </c>
@@ -8185,7 +8199,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="3">
         <v>242</v>
       </c>
@@ -8199,7 +8213,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="3">
         <v>243</v>
       </c>
@@ -8213,7 +8227,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="3">
         <v>244</v>
       </c>
@@ -8227,7 +8241,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -8241,7 +8255,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="3">
         <v>246</v>
       </c>
@@ -8255,7 +8269,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="3">
         <v>247</v>
       </c>
@@ -8269,7 +8283,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="3">
         <v>248</v>
       </c>
@@ -8283,7 +8297,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="3">
         <v>249</v>
       </c>
@@ -8297,7 +8311,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="3">
         <v>250</v>
       </c>
@@ -8311,7 +8325,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="3">
         <v>251</v>
       </c>
@@ -8325,7 +8339,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="3">
         <v>252</v>
       </c>
@@ -8339,7 +8353,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="3">
         <v>253</v>
       </c>
@@ -8353,7 +8367,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="3">
         <v>254</v>
       </c>
@@ -8367,7 +8381,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="3">
         <v>255</v>
       </c>
@@ -8381,7 +8395,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="3">
         <v>256</v>
       </c>
@@ -8395,7 +8409,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="3">
         <v>257</v>
       </c>
@@ -8409,7 +8423,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="3">
         <v>258</v>
       </c>
@@ -8423,7 +8437,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="3">
         <v>259</v>
       </c>
@@ -8437,7 +8451,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="3">
         <v>260</v>
       </c>
@@ -8451,7 +8465,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="3">
         <v>261</v>
       </c>
@@ -8465,7 +8479,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="3">
         <v>262</v>
       </c>
@@ -8479,7 +8493,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="3">
         <v>263</v>
       </c>
@@ -8493,7 +8507,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="3">
         <v>264</v>
       </c>
@@ -8507,7 +8521,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="3">
         <v>265</v>
       </c>
@@ -8521,7 +8535,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="3">
         <v>266</v>
       </c>
@@ -8535,7 +8549,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="3">
         <v>267</v>
       </c>
@@ -8549,7 +8563,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="3">
         <v>268</v>
       </c>
@@ -8563,7 +8577,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="3">
         <v>269</v>
       </c>
@@ -8577,7 +8591,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="3">
         <v>270</v>
       </c>
@@ -8591,7 +8605,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="3">
         <v>271</v>
       </c>
@@ -8605,7 +8619,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" s="3">
         <v>272</v>
       </c>
@@ -8619,7 +8633,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="3">
         <v>273</v>
       </c>
@@ -8633,7 +8647,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="3">
         <v>274</v>
       </c>
@@ -8647,7 +8661,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="3">
         <v>275</v>
       </c>
@@ -8661,7 +8675,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="3">
         <v>276</v>
       </c>
@@ -8675,7 +8689,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="3">
         <v>277</v>
       </c>
@@ -8689,7 +8703,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="3">
         <v>278</v>
       </c>
@@ -8703,7 +8717,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="3">
         <v>279</v>
       </c>
@@ -8717,7 +8731,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="3">
         <v>280</v>
       </c>
@@ -8731,7 +8745,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="3">
         <v>281</v>
       </c>
@@ -8745,7 +8759,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="3">
         <v>282</v>
       </c>
@@ -8759,7 +8773,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="3">
         <v>283</v>
       </c>
@@ -8773,7 +8787,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="3">
         <v>284</v>
       </c>
@@ -8787,7 +8801,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="3">
         <v>285</v>
       </c>
@@ -8801,7 +8815,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="3">
         <v>286</v>
       </c>
@@ -8815,7 +8829,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="3">
         <v>287</v>
       </c>
@@ -8829,7 +8843,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="3">
         <v>288</v>
       </c>
@@ -8843,7 +8857,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="3">
         <v>289</v>
       </c>
@@ -8857,7 +8871,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="3">
         <v>290</v>
       </c>
@@ -8871,7 +8885,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="3">
         <v>291</v>
       </c>
@@ -8885,7 +8899,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" s="3">
         <v>292</v>
       </c>
@@ -8899,7 +8913,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="3">
         <v>293</v>
       </c>
@@ -8913,7 +8927,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="3">
         <v>294</v>
       </c>
@@ -8927,7 +8941,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="3">
         <v>295</v>
       </c>
@@ -8941,7 +8955,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="3">
         <v>296</v>
       </c>
@@ -8955,7 +8969,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="3">
         <v>297</v>
       </c>
@@ -8969,7 +8983,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="3">
         <v>298</v>
       </c>
@@ -8983,7 +8997,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="3">
         <v>299</v>
       </c>
@@ -8997,7 +9011,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" s="3">
         <v>300</v>
       </c>
@@ -9011,7 +9025,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="3">
         <v>301</v>
       </c>
@@ -9025,7 +9039,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="3">
         <v>302</v>
       </c>
@@ -9039,7 +9053,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" s="3">
         <v>303</v>
       </c>
@@ -9053,7 +9067,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A305" s="3">
         <v>304</v>
       </c>
@@ -9067,7 +9081,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A306" s="3">
         <v>305</v>
       </c>
@@ -9081,7 +9095,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A307" s="3">
         <v>306</v>
       </c>
@@ -9095,7 +9109,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A308" s="3">
         <v>307</v>
       </c>
@@ -9109,7 +9123,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A309" s="3">
         <v>308</v>
       </c>
@@ -9123,7 +9137,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A310" s="3">
         <v>309</v>
       </c>
@@ -9137,7 +9151,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A311" s="3">
         <v>310</v>
       </c>
@@ -9151,7 +9165,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A312" s="3">
         <v>311</v>
       </c>
@@ -9165,7 +9179,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A313" s="3">
         <v>312</v>
       </c>
@@ -9179,7 +9193,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A314" s="3">
         <v>313</v>
       </c>
@@ -9193,7 +9207,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A315" s="3">
         <v>314</v>
       </c>
@@ -9207,7 +9221,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A316" s="3">
         <v>315</v>
       </c>
@@ -9221,7 +9235,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A317" s="3">
         <v>316</v>
       </c>
@@ -9235,7 +9249,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A318" s="3">
         <v>317</v>
       </c>
@@ -9249,7 +9263,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A319" s="3">
         <v>318</v>
       </c>
@@ -9263,7 +9277,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A320" s="3">
         <v>319</v>
       </c>
@@ -9277,7 +9291,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321" s="3">
         <v>320</v>
       </c>
@@ -9291,7 +9305,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322" s="3">
         <v>321</v>
       </c>
@@ -9305,7 +9319,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A323" s="3">
         <v>322</v>
       </c>
@@ -9319,7 +9333,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A324" s="3">
         <v>323</v>
       </c>
@@ -9333,7 +9347,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A325" s="3">
         <v>324</v>
       </c>
@@ -9347,7 +9361,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A326" s="3">
         <v>325</v>
       </c>
@@ -9361,7 +9375,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" s="3">
         <v>326</v>
       </c>
@@ -9375,7 +9389,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A328" s="3">
         <v>327</v>
       </c>
@@ -9389,7 +9403,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A329" s="3">
         <v>328</v>
       </c>
@@ -9403,7 +9417,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A330" s="3">
         <v>329</v>
       </c>
@@ -9417,7 +9431,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A331" s="3">
         <v>330</v>
       </c>
@@ -9431,7 +9445,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A332" s="3">
         <v>331</v>
       </c>
@@ -9445,7 +9459,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A333" s="3">
         <v>332</v>
       </c>
@@ -9459,7 +9473,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A334" s="3">
         <v>333</v>
       </c>
@@ -9473,7 +9487,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A335" s="3">
         <v>334</v>
       </c>
@@ -9487,7 +9501,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A336" s="3">
         <v>335</v>
       </c>
@@ -9501,7 +9515,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A337" s="3">
         <v>336</v>
       </c>
@@ -9515,7 +9529,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" s="3">
         <v>337</v>
       </c>
@@ -9529,7 +9543,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" s="3">
         <v>338</v>
       </c>
@@ -9543,7 +9557,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A340" s="3">
         <v>339</v>
       </c>
@@ -9557,7 +9571,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A341" s="3">
         <v>340</v>
       </c>
@@ -9571,7 +9585,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342" s="3">
         <v>341</v>
       </c>
@@ -9585,7 +9599,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A343" s="3">
         <v>342</v>
       </c>
@@ -9599,7 +9613,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A344" s="3">
         <v>343</v>
       </c>
@@ -9613,7 +9627,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A345" s="3">
         <v>344</v>
       </c>
@@ -9627,7 +9641,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A346" s="3">
         <v>345</v>
       </c>
@@ -9641,7 +9655,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A347" s="3">
         <v>346</v>
       </c>
@@ -9655,7 +9669,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A348" s="3">
         <v>347</v>
       </c>
@@ -9669,7 +9683,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A349" s="3">
         <v>348</v>
       </c>
@@ -9683,7 +9697,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A350" s="3">
         <v>349</v>
       </c>
@@ -9697,7 +9711,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A351" s="3">
         <v>350</v>
       </c>
@@ -9711,7 +9725,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" s="3">
         <v>351</v>
       </c>
@@ -9725,7 +9739,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A353" s="3">
         <v>352</v>
       </c>
@@ -9739,7 +9753,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A354" s="3">
         <v>353</v>
       </c>
@@ -9753,7 +9767,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A355" s="3">
         <v>354</v>
       </c>
@@ -9767,7 +9781,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A356" s="3">
         <v>355</v>
       </c>
@@ -9781,7 +9795,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A357" s="3">
         <v>356</v>
       </c>
@@ -9795,7 +9809,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A358" s="3">
         <v>357</v>
       </c>
@@ -9809,7 +9823,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A359" s="3">
         <v>358</v>
       </c>
@@ -9823,7 +9837,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A360" s="3">
         <v>359</v>
       </c>
@@ -9837,7 +9851,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A361" s="3">
         <v>360</v>
       </c>
@@ -9851,7 +9865,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" s="3">
         <v>361</v>
       </c>
@@ -9865,7 +9879,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A363" s="3">
         <v>362</v>
       </c>
@@ -9879,7 +9893,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A364" s="3">
         <v>363</v>
       </c>
@@ -9893,7 +9907,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" s="3">
         <v>364</v>
       </c>
@@ -9907,7 +9921,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A366" s="3">
         <v>365</v>
       </c>
@@ -9921,7 +9935,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A367" s="3">
         <v>366</v>
       </c>
@@ -9935,7 +9949,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A368" s="3">
         <v>367</v>
       </c>
@@ -9949,7 +9963,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A369" s="3">
         <v>368</v>
       </c>
@@ -9963,7 +9977,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A370" s="3">
         <v>369</v>
       </c>
@@ -9977,7 +9991,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A371" s="3">
         <v>370</v>
       </c>
@@ -9991,7 +10005,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A372" s="3">
         <v>371</v>
       </c>
@@ -10005,7 +10019,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A373" s="3">
         <v>372</v>
       </c>
@@ -10019,7 +10033,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A374" s="3">
         <v>373</v>
       </c>
@@ -10033,7 +10047,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A375" s="3">
         <v>374</v>
       </c>
@@ -10047,7 +10061,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A376" s="3">
         <v>375</v>
       </c>
@@ -10061,7 +10075,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A377" s="3">
         <v>376</v>
       </c>
@@ -10075,7 +10089,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A378" s="3">
         <v>377</v>
       </c>
@@ -10089,7 +10103,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A379" s="3">
         <v>378</v>
       </c>
@@ -10103,7 +10117,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A380" s="3">
         <v>379</v>
       </c>
@@ -10117,7 +10131,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A381" s="3">
         <v>380</v>
       </c>
@@ -10131,7 +10145,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A382" s="3">
         <v>381</v>
       </c>
@@ -10145,7 +10159,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A383" s="3">
         <v>382</v>
       </c>
@@ -10159,7 +10173,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A384" s="3">
         <v>383</v>
       </c>
@@ -10173,7 +10187,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" s="3">
         <v>384</v>
       </c>
@@ -10187,7 +10201,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" s="3">
         <v>385</v>
       </c>
@@ -10201,7 +10215,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" s="3">
         <v>386</v>
       </c>
@@ -10215,7 +10229,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" s="3">
         <v>387</v>
       </c>
@@ -10229,7 +10243,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" s="3">
         <v>388</v>
       </c>
@@ -10243,7 +10257,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" s="3">
         <v>389</v>
       </c>
@@ -10257,7 +10271,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" s="3">
         <v>390</v>
       </c>
@@ -10271,7 +10285,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" s="3">
         <v>391</v>
       </c>
@@ -10285,7 +10299,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" s="3">
         <v>392</v>
       </c>
@@ -10299,7 +10313,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" s="3">
         <v>393</v>
       </c>
@@ -10313,7 +10327,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" s="3">
         <v>394</v>
       </c>
@@ -10327,7 +10341,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" s="3">
         <v>395</v>
       </c>
@@ -10341,7 +10355,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" s="3">
         <v>396</v>
       </c>
@@ -10355,7 +10369,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" s="3">
         <v>397</v>
       </c>
@@ -10369,7 +10383,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" s="3">
         <v>398</v>
       </c>
@@ -10383,7 +10397,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" s="3">
         <v>399</v>
       </c>
@@ -10397,7 +10411,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" s="3">
         <v>400</v>
       </c>
@@ -10411,7 +10425,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" s="3">
         <v>401</v>
       </c>
@@ -10425,7 +10439,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" s="3">
         <v>402</v>
       </c>
@@ -10439,7 +10453,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" s="3">
         <v>403</v>
       </c>
@@ -10453,7 +10467,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" s="3">
         <v>404</v>
       </c>
@@ -10467,7 +10481,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" s="3">
         <v>405</v>
       </c>
@@ -10481,7 +10495,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" s="3">
         <v>406</v>
       </c>
@@ -10495,7 +10509,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" s="3">
         <v>407</v>
       </c>
@@ -10509,7 +10523,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" s="3">
         <v>408</v>
       </c>
@@ -10523,7 +10537,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" s="3">
         <v>409</v>
       </c>
@@ -10537,7 +10551,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" s="3">
         <v>410</v>
       </c>
@@ -10551,7 +10565,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" s="3">
         <v>411</v>
       </c>
@@ -10565,7 +10579,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" s="3">
         <v>412</v>
       </c>
@@ -10579,7 +10593,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" s="3">
         <v>413</v>
       </c>
@@ -10593,7 +10607,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" s="3">
         <v>414</v>
       </c>
@@ -10607,7 +10621,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" s="3">
         <v>415</v>
       </c>
@@ -10621,7 +10635,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" s="3">
         <v>416</v>
       </c>
@@ -10635,7 +10649,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" s="3">
         <v>417</v>
       </c>
@@ -10649,7 +10663,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" s="3">
         <v>418</v>
       </c>
@@ -10663,7 +10677,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" s="3">
         <v>419</v>
       </c>
@@ -10677,7 +10691,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" s="3">
         <v>420</v>
       </c>
@@ -10691,7 +10705,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" s="3">
         <v>421</v>
       </c>
@@ -10705,7 +10719,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" s="3">
         <v>422</v>
       </c>
@@ -10719,7 +10733,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" s="3">
         <v>423</v>
       </c>
@@ -10733,7 +10747,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" s="3">
         <v>424</v>
       </c>
@@ -10747,7 +10761,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" s="3">
         <v>425</v>
       </c>
@@ -10761,7 +10775,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" s="3">
         <v>426</v>
       </c>
@@ -10775,7 +10789,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" s="3">
         <v>427</v>
       </c>
@@ -10789,7 +10803,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" s="3">
         <v>428</v>
       </c>
@@ -10803,7 +10817,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" s="3">
         <v>429</v>
       </c>
@@ -10817,7 +10831,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A431" s="3">
         <v>430</v>
       </c>
@@ -10831,7 +10845,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A432" s="3">
         <v>431</v>
       </c>
@@ -10845,7 +10859,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" s="3">
         <v>432</v>
       </c>
@@ -10859,7 +10873,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" s="3">
         <v>433</v>
       </c>
@@ -10873,7 +10887,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" s="3">
         <v>434</v>
       </c>
@@ -10887,7 +10901,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" s="3">
         <v>435</v>
       </c>
@@ -10901,7 +10915,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" s="3">
         <v>436</v>
       </c>
@@ -10915,7 +10929,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" s="3">
         <v>437</v>
       </c>
@@ -10929,7 +10943,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A439" s="3">
         <v>438</v>
       </c>
@@ -10943,7 +10957,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="440" spans="1:7">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A440" s="3">
         <v>439</v>
       </c>
@@ -10957,7 +10971,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="441" spans="1:7">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A441" s="3">
         <v>440</v>
       </c>
@@ -10971,7 +10985,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A442" s="3">
         <v>441</v>
       </c>
@@ -10985,7 +10999,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="443" spans="1:7">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A443" s="3">
         <v>442</v>
       </c>
@@ -10999,7 +11013,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="444" spans="1:7">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A444" s="3">
         <v>443</v>
       </c>
@@ -11013,7 +11027,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="445" spans="1:7">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A445" s="3">
         <v>444</v>
       </c>
@@ -11027,7 +11041,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="446" spans="1:7">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A446" s="3">
         <v>445</v>
       </c>
@@ -11041,7 +11055,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A447" s="3">
         <v>446</v>
       </c>
@@ -11055,7 +11069,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A448" s="3">
         <v>447</v>
       </c>
@@ -11069,7 +11083,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A449" s="3">
         <v>448</v>
       </c>
@@ -11083,7 +11097,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A450" s="3">
         <v>449</v>
       </c>
@@ -11097,7 +11111,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A451" s="3">
         <v>450</v>
       </c>
@@ -11111,7 +11125,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="452" spans="1:7">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A452" s="3">
         <v>451</v>
       </c>
@@ -11125,7 +11139,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="453" spans="1:7">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A453" s="3">
         <v>452</v>
       </c>
@@ -11139,7 +11153,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="454" spans="1:7">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A454" s="3">
         <v>453</v>
       </c>
@@ -11153,7 +11167,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="455" spans="1:7">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A455" s="3">
         <v>454</v>
       </c>
@@ -11167,7 +11181,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A456" s="3">
         <v>455</v>
       </c>
@@ -11181,7 +11195,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="457" spans="1:7">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A457" s="3">
         <v>456</v>
       </c>
@@ -11195,7 +11209,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="458" spans="1:7">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A458" s="3">
         <v>457</v>
       </c>
@@ -11209,7 +11223,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="459" spans="1:7">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A459" s="3">
         <v>458</v>
       </c>
@@ -11223,7 +11237,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A460" s="3">
         <v>459</v>
       </c>
@@ -11237,7 +11251,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A461" s="3">
         <v>460</v>
       </c>
@@ -11251,7 +11265,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="462" spans="1:7">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A462" s="3">
         <v>461</v>
       </c>
@@ -11265,7 +11279,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="463" spans="1:7">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A463" s="3">
         <v>462</v>
       </c>
@@ -11279,7 +11293,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="464" spans="1:7">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A464" s="3">
         <v>463</v>
       </c>
@@ -11293,7 +11307,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="465" spans="1:7">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A465" s="3">
         <v>464</v>
       </c>
@@ -11307,7 +11321,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="466" spans="1:7">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A466" s="3">
         <v>465</v>
       </c>
@@ -11321,7 +11335,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="467" spans="1:7">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A467" s="3">
         <v>466</v>
       </c>
@@ -11335,7 +11349,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="468" spans="1:7">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A468" s="3">
         <v>467</v>
       </c>
@@ -11349,7 +11363,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="469" spans="1:7">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A469" s="3">
         <v>468</v>
       </c>
@@ -11363,7 +11377,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="470" spans="1:7">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A470" s="3">
         <v>469</v>
       </c>
@@ -11377,7 +11391,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="471" spans="1:7">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A471" s="3">
         <v>470</v>
       </c>
@@ -11391,7 +11405,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="472" spans="1:7">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A472" s="3">
         <v>471</v>
       </c>
@@ -11405,7 +11419,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="473" spans="1:7">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A473" s="3">
         <v>472</v>
       </c>
@@ -11419,7 +11433,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="474" spans="1:7">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A474" s="3">
         <v>473</v>
       </c>
@@ -11433,7 +11447,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="475" spans="1:7">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A475" s="3">
         <v>474</v>
       </c>
@@ -11447,7 +11461,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="476" spans="1:7">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A476" s="3">
         <v>475</v>
       </c>
@@ -11461,7 +11475,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="477" spans="1:7">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A477" s="3">
         <v>476</v>
       </c>
@@ -11475,7 +11489,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="478" spans="1:7">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A478" s="3">
         <v>477</v>
       </c>
@@ -11489,7 +11503,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="479" spans="1:7">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A479" s="3">
         <v>478</v>
       </c>
@@ -11503,7 +11517,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="480" spans="1:7">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A480" s="3">
         <v>479</v>
       </c>
@@ -11517,7 +11531,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="481" spans="1:7">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A481" s="3">
         <v>480</v>
       </c>
@@ -11531,7 +11545,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="482" spans="1:7">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A482" s="3">
         <v>481</v>
       </c>
@@ -11545,7 +11559,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="483" spans="1:7">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A483" s="3">
         <v>482</v>
       </c>
@@ -11559,7 +11573,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="484" spans="1:7">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A484" s="3">
         <v>483</v>
       </c>
@@ -11573,7 +11587,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="485" spans="1:7">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A485" s="3">
         <v>484</v>
       </c>
@@ -11587,7 +11601,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="486" spans="1:7">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A486" s="3">
         <v>485</v>
       </c>
@@ -11601,7 +11615,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="487" spans="1:7">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A487" s="3">
         <v>486</v>
       </c>
@@ -11615,7 +11629,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="488" spans="1:7">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A488" s="3">
         <v>487</v>
       </c>
@@ -11629,7 +11643,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="489" spans="1:7">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A489" s="3">
         <v>488</v>
       </c>
@@ -11643,7 +11657,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="490" spans="1:7">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A490" s="3">
         <v>489</v>
       </c>
@@ -11657,7 +11671,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="491" spans="1:7">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A491" s="3">
         <v>490</v>
       </c>
@@ -11671,7 +11685,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="492" spans="1:7">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A492" s="3">
         <v>491</v>
       </c>
@@ -11685,7 +11699,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="493" spans="1:7">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A493" s="3">
         <v>492</v>
       </c>
@@ -11699,7 +11713,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="494" spans="1:7">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A494" s="3">
         <v>493</v>
       </c>
@@ -11713,7 +11727,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="495" spans="1:7">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A495" s="3">
         <v>494</v>
       </c>
@@ -11727,7 +11741,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="496" spans="1:7">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A496" s="3">
         <v>495</v>
       </c>
@@ -11741,7 +11755,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="497" spans="1:7">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A497" s="3">
         <v>496</v>
       </c>
@@ -11755,7 +11769,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="498" spans="1:7">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A498" s="3">
         <v>497</v>
       </c>
@@ -11769,7 +11783,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="499" spans="1:7">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A499" s="3">
         <v>498</v>
       </c>
@@ -11783,7 +11797,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="500" spans="1:7">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A500" s="3">
         <v>499</v>
       </c>
@@ -11797,7 +11811,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="501" spans="1:7">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A501" s="3">
         <v>500</v>
       </c>
@@ -11811,1504 +11825,1505 @@
         <v>577</v>
       </c>
     </row>
-    <row r="502" spans="1:7">
-      <c r="A502" s="5"/>
-    </row>
-    <row r="503" spans="1:7">
-      <c r="A503" s="5"/>
-    </row>
-    <row r="504" spans="1:7">
-      <c r="A504" s="5"/>
-    </row>
-    <row r="505" spans="1:7">
-      <c r="A505" s="5"/>
-    </row>
-    <row r="506" spans="1:7">
-      <c r="A506" s="5"/>
-    </row>
-    <row r="507" spans="1:7">
-      <c r="A507" s="5"/>
-    </row>
-    <row r="508" spans="1:7">
-      <c r="A508" s="5"/>
-    </row>
-    <row r="509" spans="1:7">
-      <c r="A509" s="5"/>
-    </row>
-    <row r="510" spans="1:7">
-      <c r="A510" s="5"/>
-    </row>
-    <row r="511" spans="1:7">
-      <c r="A511" s="5"/>
-    </row>
-    <row r="512" spans="1:7">
-      <c r="A512" s="5"/>
-    </row>
-    <row r="513" spans="1:1">
-      <c r="A513" s="5"/>
-    </row>
-    <row r="514" spans="1:1">
-      <c r="A514" s="5"/>
-    </row>
-    <row r="515" spans="1:1">
-      <c r="A515" s="5"/>
-    </row>
-    <row r="516" spans="1:1">
-      <c r="A516" s="5"/>
-    </row>
-    <row r="517" spans="1:1">
-      <c r="A517" s="5"/>
-    </row>
-    <row r="518" spans="1:1">
-      <c r="A518" s="5"/>
-    </row>
-    <row r="519" spans="1:1">
-      <c r="A519" s="5"/>
-    </row>
-    <row r="520" spans="1:1">
-      <c r="A520" s="5"/>
-    </row>
-    <row r="521" spans="1:1">
-      <c r="A521" s="5"/>
-    </row>
-    <row r="522" spans="1:1">
-      <c r="A522" s="5"/>
-    </row>
-    <row r="523" spans="1:1">
-      <c r="A523" s="5"/>
-    </row>
-    <row r="524" spans="1:1">
-      <c r="A524" s="5"/>
-    </row>
-    <row r="525" spans="1:1">
-      <c r="A525" s="5"/>
-    </row>
-    <row r="526" spans="1:1">
-      <c r="A526" s="5"/>
-    </row>
-    <row r="527" spans="1:1">
-      <c r="A527" s="5"/>
-    </row>
-    <row r="528" spans="1:1">
-      <c r="A528" s="5"/>
-    </row>
-    <row r="529" spans="1:1">
-      <c r="A529" s="5"/>
-    </row>
-    <row r="530" spans="1:1">
-      <c r="A530" s="5"/>
-    </row>
-    <row r="531" spans="1:1">
-      <c r="A531" s="5"/>
-    </row>
-    <row r="532" spans="1:1">
-      <c r="A532" s="5"/>
-    </row>
-    <row r="533" spans="1:1">
-      <c r="A533" s="5"/>
-    </row>
-    <row r="534" spans="1:1">
-      <c r="A534" s="5"/>
-    </row>
-    <row r="535" spans="1:1">
-      <c r="A535" s="5"/>
-    </row>
-    <row r="536" spans="1:1">
-      <c r="A536" s="5"/>
-    </row>
-    <row r="537" spans="1:1">
-      <c r="A537" s="5"/>
-    </row>
-    <row r="538" spans="1:1">
-      <c r="A538" s="5"/>
-    </row>
-    <row r="539" spans="1:1">
-      <c r="A539" s="5"/>
-    </row>
-    <row r="540" spans="1:1">
-      <c r="A540" s="5"/>
-    </row>
-    <row r="541" spans="1:1">
-      <c r="A541" s="5"/>
-    </row>
-    <row r="542" spans="1:1">
-      <c r="A542" s="5"/>
-    </row>
-    <row r="543" spans="1:1">
-      <c r="A543" s="5"/>
-    </row>
-    <row r="544" spans="1:1">
-      <c r="A544" s="5"/>
-    </row>
-    <row r="545" spans="1:1">
-      <c r="A545" s="5"/>
-    </row>
-    <row r="546" spans="1:1">
-      <c r="A546" s="5"/>
-    </row>
-    <row r="547" spans="1:1">
-      <c r="A547" s="5"/>
-    </row>
-    <row r="548" spans="1:1">
-      <c r="A548" s="5"/>
-    </row>
-    <row r="549" spans="1:1">
-      <c r="A549" s="5"/>
-    </row>
-    <row r="550" spans="1:1">
-      <c r="A550" s="5"/>
-    </row>
-    <row r="551" spans="1:1">
-      <c r="A551" s="5"/>
-    </row>
-    <row r="552" spans="1:1">
-      <c r="A552" s="5"/>
-    </row>
-    <row r="553" spans="1:1">
-      <c r="A553" s="5"/>
-    </row>
-    <row r="554" spans="1:1">
-      <c r="A554" s="5"/>
-    </row>
-    <row r="555" spans="1:1">
-      <c r="A555" s="5"/>
-    </row>
-    <row r="556" spans="1:1">
-      <c r="A556" s="5"/>
-    </row>
-    <row r="557" spans="1:1">
-      <c r="A557" s="5"/>
-    </row>
-    <row r="558" spans="1:1">
-      <c r="A558" s="5"/>
-    </row>
-    <row r="559" spans="1:1">
-      <c r="A559" s="5"/>
-    </row>
-    <row r="560" spans="1:1">
-      <c r="A560" s="5"/>
-    </row>
-    <row r="561" spans="1:1">
-      <c r="A561" s="5"/>
-    </row>
-    <row r="562" spans="1:1">
-      <c r="A562" s="5"/>
-    </row>
-    <row r="563" spans="1:1">
-      <c r="A563" s="5"/>
-    </row>
-    <row r="564" spans="1:1">
-      <c r="A564" s="5"/>
-    </row>
-    <row r="565" spans="1:1">
-      <c r="A565" s="5"/>
-    </row>
-    <row r="566" spans="1:1">
-      <c r="A566" s="5"/>
-    </row>
-    <row r="567" spans="1:1">
-      <c r="A567" s="5"/>
-    </row>
-    <row r="568" spans="1:1">
-      <c r="A568" s="5"/>
-    </row>
-    <row r="569" spans="1:1">
-      <c r="A569" s="5"/>
-    </row>
-    <row r="570" spans="1:1">
-      <c r="A570" s="5"/>
-    </row>
-    <row r="571" spans="1:1">
-      <c r="A571" s="5"/>
-    </row>
-    <row r="572" spans="1:1">
-      <c r="A572" s="5"/>
-    </row>
-    <row r="573" spans="1:1">
-      <c r="A573" s="5"/>
-    </row>
-    <row r="574" spans="1:1">
-      <c r="A574" s="5"/>
-    </row>
-    <row r="575" spans="1:1">
-      <c r="A575" s="5"/>
-    </row>
-    <row r="576" spans="1:1">
-      <c r="A576" s="5"/>
-    </row>
-    <row r="577" spans="1:1">
-      <c r="A577" s="5"/>
-    </row>
-    <row r="578" spans="1:1">
-      <c r="A578" s="5"/>
-    </row>
-    <row r="579" spans="1:1">
-      <c r="A579" s="5"/>
-    </row>
-    <row r="580" spans="1:1">
-      <c r="A580" s="5"/>
-    </row>
-    <row r="581" spans="1:1">
-      <c r="A581" s="5"/>
-    </row>
-    <row r="582" spans="1:1">
-      <c r="A582" s="5"/>
-    </row>
-    <row r="583" spans="1:1">
-      <c r="A583" s="5"/>
-    </row>
-    <row r="584" spans="1:1">
-      <c r="A584" s="5"/>
-    </row>
-    <row r="585" spans="1:1">
-      <c r="A585" s="5"/>
-    </row>
-    <row r="586" spans="1:1">
-      <c r="A586" s="5"/>
-    </row>
-    <row r="587" spans="1:1">
-      <c r="A587" s="5"/>
-    </row>
-    <row r="588" spans="1:1">
-      <c r="A588" s="5"/>
-    </row>
-    <row r="589" spans="1:1">
-      <c r="A589" s="5"/>
-    </row>
-    <row r="590" spans="1:1">
-      <c r="A590" s="5"/>
-    </row>
-    <row r="591" spans="1:1">
-      <c r="A591" s="5"/>
-    </row>
-    <row r="592" spans="1:1">
-      <c r="A592" s="5"/>
-    </row>
-    <row r="593" spans="1:1">
-      <c r="A593" s="5"/>
-    </row>
-    <row r="594" spans="1:1">
-      <c r="A594" s="5"/>
-    </row>
-    <row r="595" spans="1:1">
-      <c r="A595" s="5"/>
-    </row>
-    <row r="596" spans="1:1">
-      <c r="A596" s="5"/>
-    </row>
-    <row r="597" spans="1:1">
-      <c r="A597" s="5"/>
-    </row>
-    <row r="598" spans="1:1">
-      <c r="A598" s="5"/>
-    </row>
-    <row r="599" spans="1:1">
-      <c r="A599" s="5"/>
-    </row>
-    <row r="600" spans="1:1">
-      <c r="A600" s="5"/>
-    </row>
-    <row r="601" spans="1:1">
-      <c r="A601" s="5"/>
-    </row>
-    <row r="602" spans="1:1">
-      <c r="A602" s="5"/>
-    </row>
-    <row r="603" spans="1:1">
-      <c r="A603" s="5"/>
-    </row>
-    <row r="604" spans="1:1">
-      <c r="A604" s="5"/>
-    </row>
-    <row r="605" spans="1:1">
-      <c r="A605" s="5"/>
-    </row>
-    <row r="606" spans="1:1">
-      <c r="A606" s="5"/>
-    </row>
-    <row r="607" spans="1:1">
-      <c r="A607" s="5"/>
-    </row>
-    <row r="608" spans="1:1">
-      <c r="A608" s="5"/>
-    </row>
-    <row r="609" spans="1:1">
-      <c r="A609" s="5"/>
-    </row>
-    <row r="610" spans="1:1">
-      <c r="A610" s="5"/>
-    </row>
-    <row r="611" spans="1:1">
-      <c r="A611" s="5"/>
-    </row>
-    <row r="612" spans="1:1">
-      <c r="A612" s="5"/>
-    </row>
-    <row r="613" spans="1:1">
-      <c r="A613" s="5"/>
-    </row>
-    <row r="614" spans="1:1">
-      <c r="A614" s="5"/>
-    </row>
-    <row r="615" spans="1:1">
-      <c r="A615" s="5"/>
-    </row>
-    <row r="616" spans="1:1">
-      <c r="A616" s="5"/>
-    </row>
-    <row r="617" spans="1:1">
-      <c r="A617" s="5"/>
-    </row>
-    <row r="618" spans="1:1">
-      <c r="A618" s="5"/>
-    </row>
-    <row r="619" spans="1:1">
-      <c r="A619" s="5"/>
-    </row>
-    <row r="620" spans="1:1">
-      <c r="A620" s="5"/>
-    </row>
-    <row r="621" spans="1:1">
-      <c r="A621" s="5"/>
-    </row>
-    <row r="622" spans="1:1">
-      <c r="A622" s="5"/>
-    </row>
-    <row r="623" spans="1:1">
-      <c r="A623" s="5"/>
-    </row>
-    <row r="624" spans="1:1">
-      <c r="A624" s="5"/>
-    </row>
-    <row r="625" spans="1:1">
-      <c r="A625" s="5"/>
-    </row>
-    <row r="626" spans="1:1">
-      <c r="A626" s="5"/>
-    </row>
-    <row r="627" spans="1:1">
-      <c r="A627" s="5"/>
-    </row>
-    <row r="628" spans="1:1">
-      <c r="A628" s="5"/>
-    </row>
-    <row r="629" spans="1:1">
-      <c r="A629" s="5"/>
-    </row>
-    <row r="630" spans="1:1">
-      <c r="A630" s="5"/>
-    </row>
-    <row r="631" spans="1:1">
-      <c r="A631" s="5"/>
-    </row>
-    <row r="632" spans="1:1">
-      <c r="A632" s="5"/>
-    </row>
-    <row r="633" spans="1:1">
-      <c r="A633" s="5"/>
-    </row>
-    <row r="634" spans="1:1">
-      <c r="A634" s="5"/>
-    </row>
-    <row r="635" spans="1:1">
-      <c r="A635" s="5"/>
-    </row>
-    <row r="636" spans="1:1">
-      <c r="A636" s="5"/>
-    </row>
-    <row r="637" spans="1:1">
-      <c r="A637" s="5"/>
-    </row>
-    <row r="638" spans="1:1">
-      <c r="A638" s="5"/>
-    </row>
-    <row r="639" spans="1:1">
-      <c r="A639" s="5"/>
-    </row>
-    <row r="640" spans="1:1">
-      <c r="A640" s="5"/>
-    </row>
-    <row r="641" spans="1:1">
-      <c r="A641" s="5"/>
-    </row>
-    <row r="642" spans="1:1">
-      <c r="A642" s="5"/>
-    </row>
-    <row r="643" spans="1:1">
-      <c r="A643" s="5"/>
-    </row>
-    <row r="644" spans="1:1">
-      <c r="A644" s="5"/>
-    </row>
-    <row r="645" spans="1:1">
-      <c r="A645" s="5"/>
-    </row>
-    <row r="646" spans="1:1">
-      <c r="A646" s="5"/>
-    </row>
-    <row r="647" spans="1:1">
-      <c r="A647" s="5"/>
-    </row>
-    <row r="648" spans="1:1">
-      <c r="A648" s="5"/>
-    </row>
-    <row r="649" spans="1:1">
-      <c r="A649" s="5"/>
-    </row>
-    <row r="650" spans="1:1">
-      <c r="A650" s="5"/>
-    </row>
-    <row r="651" spans="1:1">
-      <c r="A651" s="5"/>
-    </row>
-    <row r="652" spans="1:1">
-      <c r="A652" s="5"/>
-    </row>
-    <row r="653" spans="1:1">
-      <c r="A653" s="5"/>
-    </row>
-    <row r="654" spans="1:1">
-      <c r="A654" s="5"/>
-    </row>
-    <row r="655" spans="1:1">
-      <c r="A655" s="5"/>
-    </row>
-    <row r="656" spans="1:1">
-      <c r="A656" s="5"/>
-    </row>
-    <row r="657" spans="1:1">
-      <c r="A657" s="5"/>
-    </row>
-    <row r="658" spans="1:1">
-      <c r="A658" s="5"/>
-    </row>
-    <row r="659" spans="1:1">
-      <c r="A659" s="5"/>
-    </row>
-    <row r="660" spans="1:1">
-      <c r="A660" s="5"/>
-    </row>
-    <row r="661" spans="1:1">
-      <c r="A661" s="5"/>
-    </row>
-    <row r="662" spans="1:1">
-      <c r="A662" s="5"/>
-    </row>
-    <row r="663" spans="1:1">
-      <c r="A663" s="5"/>
-    </row>
-    <row r="664" spans="1:1">
-      <c r="A664" s="5"/>
-    </row>
-    <row r="665" spans="1:1">
-      <c r="A665" s="5"/>
-    </row>
-    <row r="666" spans="1:1">
-      <c r="A666" s="5"/>
-    </row>
-    <row r="667" spans="1:1">
-      <c r="A667" s="5"/>
-    </row>
-    <row r="668" spans="1:1">
-      <c r="A668" s="5"/>
-    </row>
-    <row r="669" spans="1:1">
-      <c r="A669" s="5"/>
-    </row>
-    <row r="670" spans="1:1">
-      <c r="A670" s="5"/>
-    </row>
-    <row r="671" spans="1:1">
-      <c r="A671" s="5"/>
-    </row>
-    <row r="672" spans="1:1">
-      <c r="A672" s="5"/>
-    </row>
-    <row r="673" spans="1:1">
-      <c r="A673" s="5"/>
-    </row>
-    <row r="674" spans="1:1">
-      <c r="A674" s="5"/>
-    </row>
-    <row r="675" spans="1:1">
-      <c r="A675" s="5"/>
-    </row>
-    <row r="676" spans="1:1">
-      <c r="A676" s="5"/>
-    </row>
-    <row r="677" spans="1:1">
-      <c r="A677" s="5"/>
-    </row>
-    <row r="678" spans="1:1">
-      <c r="A678" s="5"/>
-    </row>
-    <row r="679" spans="1:1">
-      <c r="A679" s="5"/>
-    </row>
-    <row r="680" spans="1:1">
-      <c r="A680" s="5"/>
-    </row>
-    <row r="681" spans="1:1">
-      <c r="A681" s="5"/>
-    </row>
-    <row r="682" spans="1:1">
-      <c r="A682" s="5"/>
-    </row>
-    <row r="683" spans="1:1">
-      <c r="A683" s="5"/>
-    </row>
-    <row r="684" spans="1:1">
-      <c r="A684" s="5"/>
-    </row>
-    <row r="685" spans="1:1">
-      <c r="A685" s="5"/>
-    </row>
-    <row r="686" spans="1:1">
-      <c r="A686" s="5"/>
-    </row>
-    <row r="687" spans="1:1">
-      <c r="A687" s="5"/>
-    </row>
-    <row r="688" spans="1:1">
-      <c r="A688" s="5"/>
-    </row>
-    <row r="689" spans="1:1">
-      <c r="A689" s="5"/>
-    </row>
-    <row r="690" spans="1:1">
-      <c r="A690" s="5"/>
-    </row>
-    <row r="691" spans="1:1">
-      <c r="A691" s="5"/>
-    </row>
-    <row r="692" spans="1:1">
-      <c r="A692" s="5"/>
-    </row>
-    <row r="693" spans="1:1">
-      <c r="A693" s="5"/>
-    </row>
-    <row r="694" spans="1:1">
-      <c r="A694" s="5"/>
-    </row>
-    <row r="695" spans="1:1">
-      <c r="A695" s="5"/>
-    </row>
-    <row r="696" spans="1:1">
-      <c r="A696" s="5"/>
-    </row>
-    <row r="697" spans="1:1">
-      <c r="A697" s="5"/>
-    </row>
-    <row r="698" spans="1:1">
-      <c r="A698" s="5"/>
-    </row>
-    <row r="699" spans="1:1">
-      <c r="A699" s="5"/>
-    </row>
-    <row r="700" spans="1:1">
-      <c r="A700" s="5"/>
-    </row>
-    <row r="701" spans="1:1">
-      <c r="A701" s="5"/>
-    </row>
-    <row r="702" spans="1:1">
-      <c r="A702" s="5"/>
-    </row>
-    <row r="703" spans="1:1">
-      <c r="A703" s="5"/>
-    </row>
-    <row r="704" spans="1:1">
-      <c r="A704" s="5"/>
-    </row>
-    <row r="705" spans="1:1">
-      <c r="A705" s="5"/>
-    </row>
-    <row r="706" spans="1:1">
-      <c r="A706" s="5"/>
-    </row>
-    <row r="707" spans="1:1">
-      <c r="A707" s="5"/>
-    </row>
-    <row r="708" spans="1:1">
-      <c r="A708" s="5"/>
-    </row>
-    <row r="709" spans="1:1">
-      <c r="A709" s="5"/>
-    </row>
-    <row r="710" spans="1:1">
-      <c r="A710" s="5"/>
-    </row>
-    <row r="711" spans="1:1">
-      <c r="A711" s="5"/>
-    </row>
-    <row r="712" spans="1:1">
-      <c r="A712" s="5"/>
-    </row>
-    <row r="713" spans="1:1">
-      <c r="A713" s="5"/>
-    </row>
-    <row r="714" spans="1:1">
-      <c r="A714" s="5"/>
-    </row>
-    <row r="715" spans="1:1">
-      <c r="A715" s="5"/>
-    </row>
-    <row r="716" spans="1:1">
-      <c r="A716" s="5"/>
-    </row>
-    <row r="717" spans="1:1">
-      <c r="A717" s="5"/>
-    </row>
-    <row r="718" spans="1:1">
-      <c r="A718" s="5"/>
-    </row>
-    <row r="719" spans="1:1">
-      <c r="A719" s="5"/>
-    </row>
-    <row r="720" spans="1:1">
-      <c r="A720" s="5"/>
-    </row>
-    <row r="721" spans="1:1">
-      <c r="A721" s="5"/>
-    </row>
-    <row r="722" spans="1:1">
-      <c r="A722" s="5"/>
-    </row>
-    <row r="723" spans="1:1">
-      <c r="A723" s="5"/>
-    </row>
-    <row r="724" spans="1:1">
-      <c r="A724" s="5"/>
-    </row>
-    <row r="725" spans="1:1">
-      <c r="A725" s="5"/>
-    </row>
-    <row r="726" spans="1:1">
-      <c r="A726" s="5"/>
-    </row>
-    <row r="727" spans="1:1">
-      <c r="A727" s="5"/>
-    </row>
-    <row r="728" spans="1:1">
-      <c r="A728" s="5"/>
-    </row>
-    <row r="729" spans="1:1">
-      <c r="A729" s="5"/>
-    </row>
-    <row r="730" spans="1:1">
-      <c r="A730" s="5"/>
-    </row>
-    <row r="731" spans="1:1">
-      <c r="A731" s="5"/>
-    </row>
-    <row r="732" spans="1:1">
-      <c r="A732" s="5"/>
-    </row>
-    <row r="733" spans="1:1">
-      <c r="A733" s="5"/>
-    </row>
-    <row r="734" spans="1:1">
-      <c r="A734" s="5"/>
-    </row>
-    <row r="735" spans="1:1">
-      <c r="A735" s="5"/>
-    </row>
-    <row r="736" spans="1:1">
-      <c r="A736" s="5"/>
-    </row>
-    <row r="737" spans="1:1">
-      <c r="A737" s="5"/>
-    </row>
-    <row r="738" spans="1:1">
-      <c r="A738" s="5"/>
-    </row>
-    <row r="739" spans="1:1">
-      <c r="A739" s="5"/>
-    </row>
-    <row r="740" spans="1:1">
-      <c r="A740" s="5"/>
-    </row>
-    <row r="741" spans="1:1">
-      <c r="A741" s="5"/>
-    </row>
-    <row r="742" spans="1:1">
-      <c r="A742" s="5"/>
-    </row>
-    <row r="743" spans="1:1">
-      <c r="A743" s="5"/>
-    </row>
-    <row r="744" spans="1:1">
-      <c r="A744" s="5"/>
-    </row>
-    <row r="745" spans="1:1">
-      <c r="A745" s="5"/>
-    </row>
-    <row r="746" spans="1:1">
-      <c r="A746" s="5"/>
-    </row>
-    <row r="747" spans="1:1">
-      <c r="A747" s="5"/>
-    </row>
-    <row r="748" spans="1:1">
-      <c r="A748" s="5"/>
-    </row>
-    <row r="749" spans="1:1">
-      <c r="A749" s="5"/>
-    </row>
-    <row r="750" spans="1:1">
-      <c r="A750" s="5"/>
-    </row>
-    <row r="751" spans="1:1">
-      <c r="A751" s="5"/>
-    </row>
-    <row r="752" spans="1:1">
-      <c r="A752" s="5"/>
-    </row>
-    <row r="753" spans="1:1">
-      <c r="A753" s="5"/>
-    </row>
-    <row r="754" spans="1:1">
-      <c r="A754" s="5"/>
-    </row>
-    <row r="755" spans="1:1">
-      <c r="A755" s="5"/>
-    </row>
-    <row r="756" spans="1:1">
-      <c r="A756" s="5"/>
-    </row>
-    <row r="757" spans="1:1">
-      <c r="A757" s="5"/>
-    </row>
-    <row r="758" spans="1:1">
-      <c r="A758" s="5"/>
-    </row>
-    <row r="759" spans="1:1">
-      <c r="A759" s="5"/>
-    </row>
-    <row r="760" spans="1:1">
-      <c r="A760" s="5"/>
-    </row>
-    <row r="761" spans="1:1">
-      <c r="A761" s="5"/>
-    </row>
-    <row r="762" spans="1:1">
-      <c r="A762" s="5"/>
-    </row>
-    <row r="763" spans="1:1">
-      <c r="A763" s="5"/>
-    </row>
-    <row r="764" spans="1:1">
-      <c r="A764" s="5"/>
-    </row>
-    <row r="765" spans="1:1">
-      <c r="A765" s="5"/>
-    </row>
-    <row r="766" spans="1:1">
-      <c r="A766" s="5"/>
-    </row>
-    <row r="767" spans="1:1">
-      <c r="A767" s="5"/>
-    </row>
-    <row r="768" spans="1:1">
-      <c r="A768" s="5"/>
-    </row>
-    <row r="769" spans="1:1">
-      <c r="A769" s="5"/>
-    </row>
-    <row r="770" spans="1:1">
-      <c r="A770" s="5"/>
-    </row>
-    <row r="771" spans="1:1">
-      <c r="A771" s="5"/>
-    </row>
-    <row r="772" spans="1:1">
-      <c r="A772" s="5"/>
-    </row>
-    <row r="773" spans="1:1">
-      <c r="A773" s="5"/>
-    </row>
-    <row r="774" spans="1:1">
-      <c r="A774" s="5"/>
-    </row>
-    <row r="775" spans="1:1">
-      <c r="A775" s="5"/>
-    </row>
-    <row r="776" spans="1:1">
-      <c r="A776" s="5"/>
-    </row>
-    <row r="777" spans="1:1">
-      <c r="A777" s="5"/>
-    </row>
-    <row r="778" spans="1:1">
-      <c r="A778" s="5"/>
-    </row>
-    <row r="779" spans="1:1">
-      <c r="A779" s="5"/>
-    </row>
-    <row r="780" spans="1:1">
-      <c r="A780" s="5"/>
-    </row>
-    <row r="781" spans="1:1">
-      <c r="A781" s="5"/>
-    </row>
-    <row r="782" spans="1:1">
-      <c r="A782" s="5"/>
-    </row>
-    <row r="783" spans="1:1">
-      <c r="A783" s="5"/>
-    </row>
-    <row r="784" spans="1:1">
-      <c r="A784" s="5"/>
-    </row>
-    <row r="785" spans="1:1">
-      <c r="A785" s="5"/>
-    </row>
-    <row r="786" spans="1:1">
-      <c r="A786" s="5"/>
-    </row>
-    <row r="787" spans="1:1">
-      <c r="A787" s="5"/>
-    </row>
-    <row r="788" spans="1:1">
-      <c r="A788" s="5"/>
-    </row>
-    <row r="789" spans="1:1">
-      <c r="A789" s="5"/>
-    </row>
-    <row r="790" spans="1:1">
-      <c r="A790" s="5"/>
-    </row>
-    <row r="791" spans="1:1">
-      <c r="A791" s="5"/>
-    </row>
-    <row r="792" spans="1:1">
-      <c r="A792" s="5"/>
-    </row>
-    <row r="793" spans="1:1">
-      <c r="A793" s="5"/>
-    </row>
-    <row r="794" spans="1:1">
-      <c r="A794" s="5"/>
-    </row>
-    <row r="795" spans="1:1">
-      <c r="A795" s="5"/>
-    </row>
-    <row r="796" spans="1:1">
-      <c r="A796" s="5"/>
-    </row>
-    <row r="797" spans="1:1">
-      <c r="A797" s="5"/>
-    </row>
-    <row r="798" spans="1:1">
-      <c r="A798" s="5"/>
-    </row>
-    <row r="799" spans="1:1">
-      <c r="A799" s="5"/>
-    </row>
-    <row r="800" spans="1:1">
-      <c r="A800" s="5"/>
-    </row>
-    <row r="801" spans="1:1">
-      <c r="A801" s="5"/>
-    </row>
-    <row r="802" spans="1:1">
-      <c r="A802" s="5"/>
-    </row>
-    <row r="803" spans="1:1">
-      <c r="A803" s="5"/>
-    </row>
-    <row r="804" spans="1:1">
-      <c r="A804" s="5"/>
-    </row>
-    <row r="805" spans="1:1">
-      <c r="A805" s="5"/>
-    </row>
-    <row r="806" spans="1:1">
-      <c r="A806" s="5"/>
-    </row>
-    <row r="807" spans="1:1">
-      <c r="A807" s="5"/>
-    </row>
-    <row r="808" spans="1:1">
-      <c r="A808" s="5"/>
-    </row>
-    <row r="809" spans="1:1">
-      <c r="A809" s="5"/>
-    </row>
-    <row r="810" spans="1:1">
-      <c r="A810" s="5"/>
-    </row>
-    <row r="811" spans="1:1">
-      <c r="A811" s="5"/>
-    </row>
-    <row r="812" spans="1:1">
-      <c r="A812" s="5"/>
-    </row>
-    <row r="813" spans="1:1">
-      <c r="A813" s="5"/>
-    </row>
-    <row r="814" spans="1:1">
-      <c r="A814" s="5"/>
-    </row>
-    <row r="815" spans="1:1">
-      <c r="A815" s="5"/>
-    </row>
-    <row r="816" spans="1:1">
-      <c r="A816" s="5"/>
-    </row>
-    <row r="817" spans="1:1">
-      <c r="A817" s="5"/>
-    </row>
-    <row r="818" spans="1:1">
-      <c r="A818" s="5"/>
-    </row>
-    <row r="819" spans="1:1">
-      <c r="A819" s="5"/>
-    </row>
-    <row r="820" spans="1:1">
-      <c r="A820" s="5"/>
-    </row>
-    <row r="821" spans="1:1">
-      <c r="A821" s="5"/>
-    </row>
-    <row r="822" spans="1:1">
-      <c r="A822" s="5"/>
-    </row>
-    <row r="823" spans="1:1">
-      <c r="A823" s="5"/>
-    </row>
-    <row r="824" spans="1:1">
-      <c r="A824" s="5"/>
-    </row>
-    <row r="825" spans="1:1">
-      <c r="A825" s="5"/>
-    </row>
-    <row r="826" spans="1:1">
-      <c r="A826" s="5"/>
-    </row>
-    <row r="827" spans="1:1">
-      <c r="A827" s="5"/>
-    </row>
-    <row r="828" spans="1:1">
-      <c r="A828" s="5"/>
-    </row>
-    <row r="829" spans="1:1">
-      <c r="A829" s="5"/>
-    </row>
-    <row r="830" spans="1:1">
-      <c r="A830" s="5"/>
-    </row>
-    <row r="831" spans="1:1">
-      <c r="A831" s="5"/>
-    </row>
-    <row r="832" spans="1:1">
-      <c r="A832" s="5"/>
-    </row>
-    <row r="833" spans="1:1">
-      <c r="A833" s="5"/>
-    </row>
-    <row r="834" spans="1:1">
-      <c r="A834" s="5"/>
-    </row>
-    <row r="835" spans="1:1">
-      <c r="A835" s="5"/>
-    </row>
-    <row r="836" spans="1:1">
-      <c r="A836" s="5"/>
-    </row>
-    <row r="837" spans="1:1">
-      <c r="A837" s="5"/>
-    </row>
-    <row r="838" spans="1:1">
-      <c r="A838" s="5"/>
-    </row>
-    <row r="839" spans="1:1">
-      <c r="A839" s="5"/>
-    </row>
-    <row r="840" spans="1:1">
-      <c r="A840" s="5"/>
-    </row>
-    <row r="841" spans="1:1">
-      <c r="A841" s="5"/>
-    </row>
-    <row r="842" spans="1:1">
-      <c r="A842" s="5"/>
-    </row>
-    <row r="843" spans="1:1">
-      <c r="A843" s="5"/>
-    </row>
-    <row r="844" spans="1:1">
-      <c r="A844" s="5"/>
-    </row>
-    <row r="845" spans="1:1">
-      <c r="A845" s="5"/>
-    </row>
-    <row r="846" spans="1:1">
-      <c r="A846" s="5"/>
-    </row>
-    <row r="847" spans="1:1">
-      <c r="A847" s="5"/>
-    </row>
-    <row r="848" spans="1:1">
-      <c r="A848" s="5"/>
-    </row>
-    <row r="849" spans="1:1">
-      <c r="A849" s="5"/>
-    </row>
-    <row r="850" spans="1:1">
-      <c r="A850" s="5"/>
-    </row>
-    <row r="851" spans="1:1">
-      <c r="A851" s="5"/>
-    </row>
-    <row r="852" spans="1:1">
-      <c r="A852" s="5"/>
-    </row>
-    <row r="853" spans="1:1">
-      <c r="A853" s="5"/>
-    </row>
-    <row r="854" spans="1:1">
-      <c r="A854" s="5"/>
-    </row>
-    <row r="855" spans="1:1">
-      <c r="A855" s="5"/>
-    </row>
-    <row r="856" spans="1:1">
-      <c r="A856" s="5"/>
-    </row>
-    <row r="857" spans="1:1">
-      <c r="A857" s="5"/>
-    </row>
-    <row r="858" spans="1:1">
-      <c r="A858" s="5"/>
-    </row>
-    <row r="859" spans="1:1">
-      <c r="A859" s="5"/>
-    </row>
-    <row r="860" spans="1:1">
-      <c r="A860" s="5"/>
-    </row>
-    <row r="861" spans="1:1">
-      <c r="A861" s="5"/>
-    </row>
-    <row r="862" spans="1:1">
-      <c r="A862" s="5"/>
-    </row>
-    <row r="863" spans="1:1">
-      <c r="A863" s="5"/>
-    </row>
-    <row r="864" spans="1:1">
-      <c r="A864" s="5"/>
-    </row>
-    <row r="865" spans="1:1">
-      <c r="A865" s="5"/>
-    </row>
-    <row r="866" spans="1:1">
-      <c r="A866" s="5"/>
-    </row>
-    <row r="867" spans="1:1">
-      <c r="A867" s="5"/>
-    </row>
-    <row r="868" spans="1:1">
-      <c r="A868" s="5"/>
-    </row>
-    <row r="869" spans="1:1">
-      <c r="A869" s="5"/>
-    </row>
-    <row r="870" spans="1:1">
-      <c r="A870" s="5"/>
-    </row>
-    <row r="871" spans="1:1">
-      <c r="A871" s="5"/>
-    </row>
-    <row r="872" spans="1:1">
-      <c r="A872" s="5"/>
-    </row>
-    <row r="873" spans="1:1">
-      <c r="A873" s="5"/>
-    </row>
-    <row r="874" spans="1:1">
-      <c r="A874" s="5"/>
-    </row>
-    <row r="875" spans="1:1">
-      <c r="A875" s="5"/>
-    </row>
-    <row r="876" spans="1:1">
-      <c r="A876" s="5"/>
-    </row>
-    <row r="877" spans="1:1">
-      <c r="A877" s="5"/>
-    </row>
-    <row r="878" spans="1:1">
-      <c r="A878" s="5"/>
-    </row>
-    <row r="879" spans="1:1">
-      <c r="A879" s="5"/>
-    </row>
-    <row r="880" spans="1:1">
-      <c r="A880" s="5"/>
-    </row>
-    <row r="881" spans="1:1">
-      <c r="A881" s="5"/>
-    </row>
-    <row r="882" spans="1:1">
-      <c r="A882" s="5"/>
-    </row>
-    <row r="883" spans="1:1">
-      <c r="A883" s="5"/>
-    </row>
-    <row r="884" spans="1:1">
-      <c r="A884" s="5"/>
-    </row>
-    <row r="885" spans="1:1">
-      <c r="A885" s="5"/>
-    </row>
-    <row r="886" spans="1:1">
-      <c r="A886" s="5"/>
-    </row>
-    <row r="887" spans="1:1">
-      <c r="A887" s="5"/>
-    </row>
-    <row r="888" spans="1:1">
-      <c r="A888" s="5"/>
-    </row>
-    <row r="889" spans="1:1">
-      <c r="A889" s="5"/>
-    </row>
-    <row r="890" spans="1:1">
-      <c r="A890" s="5"/>
-    </row>
-    <row r="891" spans="1:1">
-      <c r="A891" s="5"/>
-    </row>
-    <row r="892" spans="1:1">
-      <c r="A892" s="5"/>
-    </row>
-    <row r="893" spans="1:1">
-      <c r="A893" s="5"/>
-    </row>
-    <row r="894" spans="1:1">
-      <c r="A894" s="5"/>
-    </row>
-    <row r="895" spans="1:1">
-      <c r="A895" s="5"/>
-    </row>
-    <row r="896" spans="1:1">
-      <c r="A896" s="5"/>
-    </row>
-    <row r="897" spans="1:1">
-      <c r="A897" s="5"/>
-    </row>
-    <row r="898" spans="1:1">
-      <c r="A898" s="5"/>
-    </row>
-    <row r="899" spans="1:1">
-      <c r="A899" s="5"/>
-    </row>
-    <row r="900" spans="1:1">
-      <c r="A900" s="5"/>
-    </row>
-    <row r="901" spans="1:1">
-      <c r="A901" s="5"/>
-    </row>
-    <row r="902" spans="1:1">
-      <c r="A902" s="5"/>
-    </row>
-    <row r="903" spans="1:1">
-      <c r="A903" s="5"/>
-    </row>
-    <row r="904" spans="1:1">
-      <c r="A904" s="5"/>
-    </row>
-    <row r="905" spans="1:1">
-      <c r="A905" s="5"/>
-    </row>
-    <row r="906" spans="1:1">
-      <c r="A906" s="5"/>
-    </row>
-    <row r="907" spans="1:1">
-      <c r="A907" s="5"/>
-    </row>
-    <row r="908" spans="1:1">
-      <c r="A908" s="5"/>
-    </row>
-    <row r="909" spans="1:1">
-      <c r="A909" s="5"/>
-    </row>
-    <row r="910" spans="1:1">
-      <c r="A910" s="5"/>
-    </row>
-    <row r="911" spans="1:1">
-      <c r="A911" s="5"/>
-    </row>
-    <row r="912" spans="1:1">
-      <c r="A912" s="5"/>
-    </row>
-    <row r="913" spans="1:1">
-      <c r="A913" s="5"/>
-    </row>
-    <row r="914" spans="1:1">
-      <c r="A914" s="5"/>
-    </row>
-    <row r="915" spans="1:1">
-      <c r="A915" s="5"/>
-    </row>
-    <row r="916" spans="1:1">
-      <c r="A916" s="5"/>
-    </row>
-    <row r="917" spans="1:1">
-      <c r="A917" s="5"/>
-    </row>
-    <row r="918" spans="1:1">
-      <c r="A918" s="5"/>
-    </row>
-    <row r="919" spans="1:1">
-      <c r="A919" s="5"/>
-    </row>
-    <row r="920" spans="1:1">
-      <c r="A920" s="5"/>
-    </row>
-    <row r="921" spans="1:1">
-      <c r="A921" s="5"/>
-    </row>
-    <row r="922" spans="1:1">
-      <c r="A922" s="5"/>
-    </row>
-    <row r="923" spans="1:1">
-      <c r="A923" s="5"/>
-    </row>
-    <row r="924" spans="1:1">
-      <c r="A924" s="5"/>
-    </row>
-    <row r="925" spans="1:1">
-      <c r="A925" s="5"/>
-    </row>
-    <row r="926" spans="1:1">
-      <c r="A926" s="5"/>
-    </row>
-    <row r="927" spans="1:1">
-      <c r="A927" s="5"/>
-    </row>
-    <row r="928" spans="1:1">
-      <c r="A928" s="5"/>
-    </row>
-    <row r="929" spans="1:1">
-      <c r="A929" s="5"/>
-    </row>
-    <row r="930" spans="1:1">
-      <c r="A930" s="5"/>
-    </row>
-    <row r="931" spans="1:1">
-      <c r="A931" s="5"/>
-    </row>
-    <row r="932" spans="1:1">
-      <c r="A932" s="5"/>
-    </row>
-    <row r="933" spans="1:1">
-      <c r="A933" s="5"/>
-    </row>
-    <row r="934" spans="1:1">
-      <c r="A934" s="5"/>
-    </row>
-    <row r="935" spans="1:1">
-      <c r="A935" s="5"/>
-    </row>
-    <row r="936" spans="1:1">
-      <c r="A936" s="5"/>
-    </row>
-    <row r="937" spans="1:1">
-      <c r="A937" s="5"/>
-    </row>
-    <row r="938" spans="1:1">
-      <c r="A938" s="5"/>
-    </row>
-    <row r="939" spans="1:1">
-      <c r="A939" s="5"/>
-    </row>
-    <row r="940" spans="1:1">
-      <c r="A940" s="5"/>
-    </row>
-    <row r="941" spans="1:1">
-      <c r="A941" s="5"/>
-    </row>
-    <row r="942" spans="1:1">
-      <c r="A942" s="5"/>
-    </row>
-    <row r="943" spans="1:1">
-      <c r="A943" s="5"/>
-    </row>
-    <row r="944" spans="1:1">
-      <c r="A944" s="5"/>
-    </row>
-    <row r="945" spans="1:1">
-      <c r="A945" s="5"/>
-    </row>
-    <row r="946" spans="1:1">
-      <c r="A946" s="5"/>
-    </row>
-    <row r="947" spans="1:1">
-      <c r="A947" s="5"/>
-    </row>
-    <row r="948" spans="1:1">
-      <c r="A948" s="5"/>
-    </row>
-    <row r="949" spans="1:1">
-      <c r="A949" s="5"/>
-    </row>
-    <row r="950" spans="1:1">
-      <c r="A950" s="5"/>
-    </row>
-    <row r="951" spans="1:1">
-      <c r="A951" s="5"/>
-    </row>
-    <row r="952" spans="1:1">
-      <c r="A952" s="5"/>
-    </row>
-    <row r="953" spans="1:1">
-      <c r="A953" s="5"/>
-    </row>
-    <row r="954" spans="1:1">
-      <c r="A954" s="5"/>
-    </row>
-    <row r="955" spans="1:1">
-      <c r="A955" s="5"/>
-    </row>
-    <row r="956" spans="1:1">
-      <c r="A956" s="5"/>
-    </row>
-    <row r="957" spans="1:1">
-      <c r="A957" s="5"/>
-    </row>
-    <row r="958" spans="1:1">
-      <c r="A958" s="5"/>
-    </row>
-    <row r="959" spans="1:1">
-      <c r="A959" s="5"/>
-    </row>
-    <row r="960" spans="1:1">
-      <c r="A960" s="5"/>
-    </row>
-    <row r="961" spans="1:1">
-      <c r="A961" s="5"/>
-    </row>
-    <row r="962" spans="1:1">
-      <c r="A962" s="5"/>
-    </row>
-    <row r="963" spans="1:1">
-      <c r="A963" s="5"/>
-    </row>
-    <row r="964" spans="1:1">
-      <c r="A964" s="5"/>
-    </row>
-    <row r="965" spans="1:1">
-      <c r="A965" s="5"/>
-    </row>
-    <row r="966" spans="1:1">
-      <c r="A966" s="5"/>
-    </row>
-    <row r="967" spans="1:1">
-      <c r="A967" s="5"/>
-    </row>
-    <row r="968" spans="1:1">
-      <c r="A968" s="5"/>
-    </row>
-    <row r="969" spans="1:1">
-      <c r="A969" s="5"/>
-    </row>
-    <row r="970" spans="1:1">
-      <c r="A970" s="5"/>
-    </row>
-    <row r="971" spans="1:1">
-      <c r="A971" s="5"/>
-    </row>
-    <row r="972" spans="1:1">
-      <c r="A972" s="5"/>
-    </row>
-    <row r="973" spans="1:1">
-      <c r="A973" s="5"/>
-    </row>
-    <row r="974" spans="1:1">
-      <c r="A974" s="5"/>
-    </row>
-    <row r="975" spans="1:1">
-      <c r="A975" s="5"/>
-    </row>
-    <row r="976" spans="1:1">
-      <c r="A976" s="5"/>
-    </row>
-    <row r="977" spans="1:1">
-      <c r="A977" s="5"/>
-    </row>
-    <row r="978" spans="1:1">
-      <c r="A978" s="5"/>
-    </row>
-    <row r="979" spans="1:1">
-      <c r="A979" s="5"/>
-    </row>
-    <row r="980" spans="1:1">
-      <c r="A980" s="5"/>
-    </row>
-    <row r="981" spans="1:1">
-      <c r="A981" s="5"/>
-    </row>
-    <row r="982" spans="1:1">
-      <c r="A982" s="5"/>
-    </row>
-    <row r="983" spans="1:1">
-      <c r="A983" s="5"/>
-    </row>
-    <row r="984" spans="1:1">
-      <c r="A984" s="5"/>
-    </row>
-    <row r="985" spans="1:1">
-      <c r="A985" s="5"/>
-    </row>
-    <row r="986" spans="1:1">
-      <c r="A986" s="5"/>
-    </row>
-    <row r="987" spans="1:1">
-      <c r="A987" s="5"/>
-    </row>
-    <row r="988" spans="1:1">
-      <c r="A988" s="5"/>
-    </row>
-    <row r="989" spans="1:1">
-      <c r="A989" s="5"/>
-    </row>
-    <row r="990" spans="1:1">
-      <c r="A990" s="5"/>
-    </row>
-    <row r="991" spans="1:1">
-      <c r="A991" s="5"/>
-    </row>
-    <row r="992" spans="1:1">
-      <c r="A992" s="5"/>
-    </row>
-    <row r="993" spans="1:1">
-      <c r="A993" s="5"/>
-    </row>
-    <row r="994" spans="1:1">
-      <c r="A994" s="5"/>
-    </row>
-    <row r="995" spans="1:1">
-      <c r="A995" s="5"/>
-    </row>
-    <row r="996" spans="1:1">
-      <c r="A996" s="5"/>
-    </row>
-    <row r="997" spans="1:1">
-      <c r="A997" s="5"/>
-    </row>
-    <row r="998" spans="1:1">
-      <c r="A998" s="5"/>
-    </row>
-    <row r="999" spans="1:1">
-      <c r="A999" s="5"/>
-    </row>
-    <row r="1000" spans="1:1">
-      <c r="A1000" s="5"/>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A502" s="3"/>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A503" s="3"/>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A504" s="3"/>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A505" s="3"/>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A506" s="3"/>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A507" s="3"/>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A508" s="3"/>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A509" s="3"/>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A510" s="3"/>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A511" s="3"/>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A512" s="3"/>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A513" s="3"/>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A514" s="3"/>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A515" s="3"/>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A516" s="3"/>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A517" s="3"/>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A518" s="3"/>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A519" s="3"/>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A520" s="3"/>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A521" s="3"/>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A522" s="3"/>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A523" s="3"/>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A524" s="3"/>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A525" s="3"/>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A526" s="3"/>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A527" s="3"/>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A528" s="3"/>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A529" s="3"/>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A530" s="3"/>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A531" s="3"/>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A532" s="3"/>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A533" s="3"/>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A534" s="3"/>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A535" s="3"/>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A536" s="3"/>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A537" s="3"/>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A538" s="3"/>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A539" s="3"/>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A540" s="3"/>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A541" s="3"/>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A542" s="3"/>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A543" s="3"/>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A544" s="3"/>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A545" s="3"/>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A546" s="3"/>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A547" s="3"/>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A548" s="3"/>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A549" s="3"/>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A550" s="3"/>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A551" s="3"/>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A552" s="3"/>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A553" s="3"/>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A554" s="3"/>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A555" s="3"/>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A556" s="3"/>
+    </row>
+    <row r="557" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A557" s="3"/>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A558" s="3"/>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A559" s="3"/>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A560" s="3"/>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A561" s="3"/>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A562" s="3"/>
+    </row>
+    <row r="563" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A563" s="3"/>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A564" s="3"/>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A565" s="3"/>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A566" s="3"/>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A567" s="3"/>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A568" s="3"/>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A569" s="3"/>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A570" s="3"/>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A571" s="3"/>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A572" s="3"/>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A573" s="3"/>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A574" s="3"/>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A575" s="3"/>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A576" s="3"/>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A577" s="3"/>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A578" s="3"/>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A579" s="3"/>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A580" s="3"/>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A581" s="3"/>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A582" s="3"/>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A583" s="3"/>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A584" s="3"/>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A585" s="3"/>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A586" s="3"/>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A587" s="3"/>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A588" s="3"/>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A589" s="3"/>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A590" s="3"/>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A591" s="3"/>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A592" s="3"/>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A593" s="3"/>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A594" s="3"/>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A595" s="3"/>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A596" s="3"/>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A597" s="3"/>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A598" s="3"/>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A599" s="3"/>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A600" s="3"/>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A601" s="3"/>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A602" s="3"/>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A603" s="3"/>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A604" s="3"/>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A605" s="3"/>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A606" s="3"/>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A607" s="3"/>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A608" s="3"/>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A609" s="3"/>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A610" s="3"/>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A611" s="3"/>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A612" s="3"/>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A613" s="3"/>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A614" s="3"/>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A615" s="3"/>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A616" s="3"/>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A617" s="3"/>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A618" s="3"/>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A619" s="3"/>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A620" s="3"/>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A621" s="3"/>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A622" s="3"/>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A623" s="3"/>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A624" s="3"/>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A625" s="3"/>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A626" s="3"/>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A627" s="3"/>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A628" s="3"/>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A629" s="3"/>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A630" s="3"/>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A631" s="3"/>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A632" s="3"/>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A633" s="3"/>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A634" s="3"/>
+    </row>
+    <row r="635" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A635" s="3"/>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A636" s="3"/>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A637" s="3"/>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A638" s="3"/>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A639" s="3"/>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A640" s="3"/>
+    </row>
+    <row r="641" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A641" s="3"/>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A642" s="3"/>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A643" s="3"/>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A644" s="3"/>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A645" s="3"/>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A646" s="3"/>
+    </row>
+    <row r="647" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A647" s="3"/>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A648" s="3"/>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A649" s="3"/>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A650" s="3"/>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A651" s="3"/>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A652" s="3"/>
+    </row>
+    <row r="653" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A653" s="3"/>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A654" s="3"/>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A655" s="3"/>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A656" s="3"/>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A657" s="3"/>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A658" s="3"/>
+    </row>
+    <row r="659" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A659" s="3"/>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A660" s="3"/>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A661" s="3"/>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A662" s="3"/>
+    </row>
+    <row r="663" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A663" s="3"/>
+    </row>
+    <row r="664" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A664" s="3"/>
+    </row>
+    <row r="665" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A665" s="3"/>
+    </row>
+    <row r="666" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A666" s="3"/>
+    </row>
+    <row r="667" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A667" s="3"/>
+    </row>
+    <row r="668" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A668" s="3"/>
+    </row>
+    <row r="669" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A669" s="3"/>
+    </row>
+    <row r="670" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A670" s="3"/>
+    </row>
+    <row r="671" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A671" s="3"/>
+    </row>
+    <row r="672" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A672" s="3"/>
+    </row>
+    <row r="673" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A673" s="3"/>
+    </row>
+    <row r="674" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A674" s="3"/>
+    </row>
+    <row r="675" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A675" s="3"/>
+    </row>
+    <row r="676" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A676" s="3"/>
+    </row>
+    <row r="677" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A677" s="3"/>
+    </row>
+    <row r="678" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A678" s="3"/>
+    </row>
+    <row r="679" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A679" s="3"/>
+    </row>
+    <row r="680" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A680" s="3"/>
+    </row>
+    <row r="681" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A681" s="3"/>
+    </row>
+    <row r="682" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A682" s="3"/>
+    </row>
+    <row r="683" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A683" s="3"/>
+    </row>
+    <row r="684" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A684" s="3"/>
+    </row>
+    <row r="685" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A685" s="3"/>
+    </row>
+    <row r="686" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A686" s="3"/>
+    </row>
+    <row r="687" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A687" s="3"/>
+    </row>
+    <row r="688" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A688" s="3"/>
+    </row>
+    <row r="689" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A689" s="3"/>
+    </row>
+    <row r="690" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A690" s="3"/>
+    </row>
+    <row r="691" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A691" s="3"/>
+    </row>
+    <row r="692" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A692" s="3"/>
+    </row>
+    <row r="693" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A693" s="3"/>
+    </row>
+    <row r="694" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A694" s="3"/>
+    </row>
+    <row r="695" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A695" s="3"/>
+    </row>
+    <row r="696" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A696" s="3"/>
+    </row>
+    <row r="697" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A697" s="3"/>
+    </row>
+    <row r="698" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A698" s="3"/>
+    </row>
+    <row r="699" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A699" s="3"/>
+    </row>
+    <row r="700" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A700" s="3"/>
+    </row>
+    <row r="701" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A701" s="3"/>
+    </row>
+    <row r="702" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A702" s="3"/>
+    </row>
+    <row r="703" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A703" s="3"/>
+    </row>
+    <row r="704" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A704" s="3"/>
+    </row>
+    <row r="705" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A705" s="3"/>
+    </row>
+    <row r="706" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A706" s="3"/>
+    </row>
+    <row r="707" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A707" s="3"/>
+    </row>
+    <row r="708" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A708" s="3"/>
+    </row>
+    <row r="709" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A709" s="3"/>
+    </row>
+    <row r="710" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A710" s="3"/>
+    </row>
+    <row r="711" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A711" s="3"/>
+    </row>
+    <row r="712" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A712" s="3"/>
+    </row>
+    <row r="713" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A713" s="3"/>
+    </row>
+    <row r="714" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A714" s="3"/>
+    </row>
+    <row r="715" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A715" s="3"/>
+    </row>
+    <row r="716" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A716" s="3"/>
+    </row>
+    <row r="717" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A717" s="3"/>
+    </row>
+    <row r="718" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A718" s="3"/>
+    </row>
+    <row r="719" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A719" s="3"/>
+    </row>
+    <row r="720" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A720" s="3"/>
+    </row>
+    <row r="721" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A721" s="3"/>
+    </row>
+    <row r="722" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A722" s="3"/>
+    </row>
+    <row r="723" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A723" s="3"/>
+    </row>
+    <row r="724" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A724" s="3"/>
+    </row>
+    <row r="725" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A725" s="3"/>
+    </row>
+    <row r="726" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A726" s="3"/>
+    </row>
+    <row r="727" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A727" s="3"/>
+    </row>
+    <row r="728" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A728" s="3"/>
+    </row>
+    <row r="729" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A729" s="3"/>
+    </row>
+    <row r="730" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A730" s="3"/>
+    </row>
+    <row r="731" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A731" s="3"/>
+    </row>
+    <row r="732" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A732" s="3"/>
+    </row>
+    <row r="733" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A733" s="3"/>
+    </row>
+    <row r="734" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A734" s="3"/>
+    </row>
+    <row r="735" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A735" s="3"/>
+    </row>
+    <row r="736" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A736" s="3"/>
+    </row>
+    <row r="737" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A737" s="3"/>
+    </row>
+    <row r="738" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A738" s="3"/>
+    </row>
+    <row r="739" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A739" s="3"/>
+    </row>
+    <row r="740" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A740" s="3"/>
+    </row>
+    <row r="741" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A741" s="3"/>
+    </row>
+    <row r="742" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A742" s="3"/>
+    </row>
+    <row r="743" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A743" s="3"/>
+    </row>
+    <row r="744" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A744" s="3"/>
+    </row>
+    <row r="745" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A745" s="3"/>
+    </row>
+    <row r="746" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A746" s="3"/>
+    </row>
+    <row r="747" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A747" s="3"/>
+    </row>
+    <row r="748" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A748" s="3"/>
+    </row>
+    <row r="749" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A749" s="3"/>
+    </row>
+    <row r="750" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A750" s="3"/>
+    </row>
+    <row r="751" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A751" s="3"/>
+    </row>
+    <row r="752" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A752" s="3"/>
+    </row>
+    <row r="753" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A753" s="3"/>
+    </row>
+    <row r="754" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A754" s="3"/>
+    </row>
+    <row r="755" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A755" s="3"/>
+    </row>
+    <row r="756" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A756" s="3"/>
+    </row>
+    <row r="757" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A757" s="3"/>
+    </row>
+    <row r="758" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A758" s="3"/>
+    </row>
+    <row r="759" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A759" s="3"/>
+    </row>
+    <row r="760" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A760" s="3"/>
+    </row>
+    <row r="761" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A761" s="3"/>
+    </row>
+    <row r="762" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A762" s="3"/>
+    </row>
+    <row r="763" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A763" s="3"/>
+    </row>
+    <row r="764" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A764" s="3"/>
+    </row>
+    <row r="765" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A765" s="3"/>
+    </row>
+    <row r="766" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A766" s="3"/>
+    </row>
+    <row r="767" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A767" s="3"/>
+    </row>
+    <row r="768" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A768" s="3"/>
+    </row>
+    <row r="769" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A769" s="3"/>
+    </row>
+    <row r="770" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A770" s="3"/>
+    </row>
+    <row r="771" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A771" s="3"/>
+    </row>
+    <row r="772" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A772" s="3"/>
+    </row>
+    <row r="773" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A773" s="3"/>
+    </row>
+    <row r="774" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A774" s="3"/>
+    </row>
+    <row r="775" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A775" s="3"/>
+    </row>
+    <row r="776" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A776" s="3"/>
+    </row>
+    <row r="777" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A777" s="3"/>
+    </row>
+    <row r="778" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A778" s="3"/>
+    </row>
+    <row r="779" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A779" s="3"/>
+    </row>
+    <row r="780" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A780" s="3"/>
+    </row>
+    <row r="781" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A781" s="3"/>
+    </row>
+    <row r="782" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A782" s="3"/>
+    </row>
+    <row r="783" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A783" s="3"/>
+    </row>
+    <row r="784" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A784" s="3"/>
+    </row>
+    <row r="785" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A785" s="3"/>
+    </row>
+    <row r="786" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A786" s="3"/>
+    </row>
+    <row r="787" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A787" s="3"/>
+    </row>
+    <row r="788" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A788" s="3"/>
+    </row>
+    <row r="789" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A789" s="3"/>
+    </row>
+    <row r="790" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A790" s="3"/>
+    </row>
+    <row r="791" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A791" s="3"/>
+    </row>
+    <row r="792" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A792" s="3"/>
+    </row>
+    <row r="793" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A793" s="3"/>
+    </row>
+    <row r="794" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A794" s="3"/>
+    </row>
+    <row r="795" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A795" s="3"/>
+    </row>
+    <row r="796" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A796" s="3"/>
+    </row>
+    <row r="797" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A797" s="3"/>
+    </row>
+    <row r="798" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A798" s="3"/>
+    </row>
+    <row r="799" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A799" s="3"/>
+    </row>
+    <row r="800" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A800" s="3"/>
+    </row>
+    <row r="801" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A801" s="3"/>
+    </row>
+    <row r="802" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A802" s="3"/>
+    </row>
+    <row r="803" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A803" s="3"/>
+    </row>
+    <row r="804" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A804" s="3"/>
+    </row>
+    <row r="805" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A805" s="3"/>
+    </row>
+    <row r="806" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A806" s="3"/>
+    </row>
+    <row r="807" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A807" s="3"/>
+    </row>
+    <row r="808" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A808" s="3"/>
+    </row>
+    <row r="809" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A809" s="3"/>
+    </row>
+    <row r="810" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A810" s="3"/>
+    </row>
+    <row r="811" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A811" s="3"/>
+    </row>
+    <row r="812" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A812" s="3"/>
+    </row>
+    <row r="813" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A813" s="3"/>
+    </row>
+    <row r="814" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A814" s="3"/>
+    </row>
+    <row r="815" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A815" s="3"/>
+    </row>
+    <row r="816" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A816" s="3"/>
+    </row>
+    <row r="817" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A817" s="3"/>
+    </row>
+    <row r="818" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A818" s="3"/>
+    </row>
+    <row r="819" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A819" s="3"/>
+    </row>
+    <row r="820" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A820" s="3"/>
+    </row>
+    <row r="821" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A821" s="3"/>
+    </row>
+    <row r="822" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A822" s="3"/>
+    </row>
+    <row r="823" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A823" s="3"/>
+    </row>
+    <row r="824" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A824" s="3"/>
+    </row>
+    <row r="825" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A825" s="3"/>
+    </row>
+    <row r="826" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A826" s="3"/>
+    </row>
+    <row r="827" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A827" s="3"/>
+    </row>
+    <row r="828" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A828" s="3"/>
+    </row>
+    <row r="829" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A829" s="3"/>
+    </row>
+    <row r="830" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A830" s="3"/>
+    </row>
+    <row r="831" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A831" s="3"/>
+    </row>
+    <row r="832" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A832" s="3"/>
+    </row>
+    <row r="833" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A833" s="3"/>
+    </row>
+    <row r="834" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A834" s="3"/>
+    </row>
+    <row r="835" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A835" s="3"/>
+    </row>
+    <row r="836" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A836" s="3"/>
+    </row>
+    <row r="837" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A837" s="3"/>
+    </row>
+    <row r="838" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A838" s="3"/>
+    </row>
+    <row r="839" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A839" s="3"/>
+    </row>
+    <row r="840" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A840" s="3"/>
+    </row>
+    <row r="841" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A841" s="3"/>
+    </row>
+    <row r="842" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A842" s="3"/>
+    </row>
+    <row r="843" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A843" s="3"/>
+    </row>
+    <row r="844" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A844" s="3"/>
+    </row>
+    <row r="845" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A845" s="3"/>
+    </row>
+    <row r="846" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A846" s="3"/>
+    </row>
+    <row r="847" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A847" s="3"/>
+    </row>
+    <row r="848" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A848" s="3"/>
+    </row>
+    <row r="849" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A849" s="3"/>
+    </row>
+    <row r="850" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A850" s="3"/>
+    </row>
+    <row r="851" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A851" s="3"/>
+    </row>
+    <row r="852" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A852" s="3"/>
+    </row>
+    <row r="853" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A853" s="3"/>
+    </row>
+    <row r="854" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A854" s="3"/>
+    </row>
+    <row r="855" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A855" s="3"/>
+    </row>
+    <row r="856" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A856" s="3"/>
+    </row>
+    <row r="857" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A857" s="3"/>
+    </row>
+    <row r="858" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A858" s="3"/>
+    </row>
+    <row r="859" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A859" s="3"/>
+    </row>
+    <row r="860" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A860" s="3"/>
+    </row>
+    <row r="861" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A861" s="3"/>
+    </row>
+    <row r="862" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A862" s="3"/>
+    </row>
+    <row r="863" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A863" s="3"/>
+    </row>
+    <row r="864" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A864" s="3"/>
+    </row>
+    <row r="865" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A865" s="3"/>
+    </row>
+    <row r="866" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A866" s="3"/>
+    </row>
+    <row r="867" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A867" s="3"/>
+    </row>
+    <row r="868" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A868" s="3"/>
+    </row>
+    <row r="869" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A869" s="3"/>
+    </row>
+    <row r="870" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A870" s="3"/>
+    </row>
+    <row r="871" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A871" s="3"/>
+    </row>
+    <row r="872" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A872" s="3"/>
+    </row>
+    <row r="873" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A873" s="3"/>
+    </row>
+    <row r="874" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A874" s="3"/>
+    </row>
+    <row r="875" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A875" s="3"/>
+    </row>
+    <row r="876" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A876" s="3"/>
+    </row>
+    <row r="877" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A877" s="3"/>
+    </row>
+    <row r="878" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A878" s="3"/>
+    </row>
+    <row r="879" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A879" s="3"/>
+    </row>
+    <row r="880" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A880" s="3"/>
+    </row>
+    <row r="881" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A881" s="3"/>
+    </row>
+    <row r="882" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A882" s="3"/>
+    </row>
+    <row r="883" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A883" s="3"/>
+    </row>
+    <row r="884" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A884" s="3"/>
+    </row>
+    <row r="885" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A885" s="3"/>
+    </row>
+    <row r="886" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A886" s="3"/>
+    </row>
+    <row r="887" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A887" s="3"/>
+    </row>
+    <row r="888" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A888" s="3"/>
+    </row>
+    <row r="889" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A889" s="3"/>
+    </row>
+    <row r="890" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A890" s="3"/>
+    </row>
+    <row r="891" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A891" s="3"/>
+    </row>
+    <row r="892" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A892" s="3"/>
+    </row>
+    <row r="893" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A893" s="3"/>
+    </row>
+    <row r="894" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A894" s="3"/>
+    </row>
+    <row r="895" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A895" s="3"/>
+    </row>
+    <row r="896" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A896" s="3"/>
+    </row>
+    <row r="897" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A897" s="3"/>
+    </row>
+    <row r="898" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A898" s="3"/>
+    </row>
+    <row r="899" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A899" s="3"/>
+    </row>
+    <row r="900" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A900" s="3"/>
+    </row>
+    <row r="901" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A901" s="3"/>
+    </row>
+    <row r="902" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A902" s="3"/>
+    </row>
+    <row r="903" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A903" s="3"/>
+    </row>
+    <row r="904" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A904" s="3"/>
+    </row>
+    <row r="905" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A905" s="3"/>
+    </row>
+    <row r="906" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A906" s="3"/>
+    </row>
+    <row r="907" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A907" s="3"/>
+    </row>
+    <row r="908" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A908" s="3"/>
+    </row>
+    <row r="909" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A909" s="3"/>
+    </row>
+    <row r="910" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A910" s="3"/>
+    </row>
+    <row r="911" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A911" s="3"/>
+    </row>
+    <row r="912" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A912" s="3"/>
+    </row>
+    <row r="913" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A913" s="3"/>
+    </row>
+    <row r="914" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A914" s="3"/>
+    </row>
+    <row r="915" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A915" s="3"/>
+    </row>
+    <row r="916" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A916" s="3"/>
+    </row>
+    <row r="917" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A917" s="3"/>
+    </row>
+    <row r="918" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A918" s="3"/>
+    </row>
+    <row r="919" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A919" s="3"/>
+    </row>
+    <row r="920" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A920" s="3"/>
+    </row>
+    <row r="921" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A921" s="3"/>
+    </row>
+    <row r="922" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A922" s="3"/>
+    </row>
+    <row r="923" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A923" s="3"/>
+    </row>
+    <row r="924" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A924" s="3"/>
+    </row>
+    <row r="925" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A925" s="3"/>
+    </row>
+    <row r="926" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A926" s="3"/>
+    </row>
+    <row r="927" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A927" s="3"/>
+    </row>
+    <row r="928" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A928" s="3"/>
+    </row>
+    <row r="929" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A929" s="3"/>
+    </row>
+    <row r="930" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A930" s="3"/>
+    </row>
+    <row r="931" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A931" s="3"/>
+    </row>
+    <row r="932" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A932" s="3"/>
+    </row>
+    <row r="933" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A933" s="3"/>
+    </row>
+    <row r="934" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A934" s="3"/>
+    </row>
+    <row r="935" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A935" s="3"/>
+    </row>
+    <row r="936" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A936" s="3"/>
+    </row>
+    <row r="937" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A937" s="3"/>
+    </row>
+    <row r="938" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A938" s="3"/>
+    </row>
+    <row r="939" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A939" s="3"/>
+    </row>
+    <row r="940" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A940" s="3"/>
+    </row>
+    <row r="941" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A941" s="3"/>
+    </row>
+    <row r="942" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A942" s="3"/>
+    </row>
+    <row r="943" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A943" s="3"/>
+    </row>
+    <row r="944" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A944" s="3"/>
+    </row>
+    <row r="945" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A945" s="3"/>
+    </row>
+    <row r="946" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A946" s="3"/>
+    </row>
+    <row r="947" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A947" s="3"/>
+    </row>
+    <row r="948" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A948" s="3"/>
+    </row>
+    <row r="949" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A949" s="3"/>
+    </row>
+    <row r="950" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A950" s="3"/>
+    </row>
+    <row r="951" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A951" s="3"/>
+    </row>
+    <row r="952" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A952" s="3"/>
+    </row>
+    <row r="953" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A953" s="3"/>
+    </row>
+    <row r="954" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A954" s="3"/>
+    </row>
+    <row r="955" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A955" s="3"/>
+    </row>
+    <row r="956" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A956" s="3"/>
+    </row>
+    <row r="957" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A957" s="3"/>
+    </row>
+    <row r="958" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A958" s="3"/>
+    </row>
+    <row r="959" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A959" s="3"/>
+    </row>
+    <row r="960" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A960" s="3"/>
+    </row>
+    <row r="961" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A961" s="3"/>
+    </row>
+    <row r="962" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A962" s="3"/>
+    </row>
+    <row r="963" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A963" s="3"/>
+    </row>
+    <row r="964" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A964" s="3"/>
+    </row>
+    <row r="965" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A965" s="3"/>
+    </row>
+    <row r="966" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A966" s="3"/>
+    </row>
+    <row r="967" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A967" s="3"/>
+    </row>
+    <row r="968" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A968" s="3"/>
+    </row>
+    <row r="969" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A969" s="3"/>
+    </row>
+    <row r="970" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A970" s="3"/>
+    </row>
+    <row r="971" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A971" s="3"/>
+    </row>
+    <row r="972" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A972" s="3"/>
+    </row>
+    <row r="973" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A973" s="3"/>
+    </row>
+    <row r="974" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A974" s="3"/>
+    </row>
+    <row r="975" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A975" s="3"/>
+    </row>
+    <row r="976" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A976" s="3"/>
+    </row>
+    <row r="977" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A977" s="3"/>
+    </row>
+    <row r="978" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A978" s="3"/>
+    </row>
+    <row r="979" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A979" s="3"/>
+    </row>
+    <row r="980" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A980" s="3"/>
+    </row>
+    <row r="981" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A981" s="3"/>
+    </row>
+    <row r="982" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A982" s="3"/>
+    </row>
+    <row r="983" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A983" s="3"/>
+    </row>
+    <row r="984" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A984" s="3"/>
+    </row>
+    <row r="985" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A985" s="3"/>
+    </row>
+    <row r="986" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A986" s="3"/>
+    </row>
+    <row r="987" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A987" s="3"/>
+    </row>
+    <row r="988" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A988" s="3"/>
+    </row>
+    <row r="989" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A989" s="3"/>
+    </row>
+    <row r="990" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A990" s="3"/>
+    </row>
+    <row r="991" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A991" s="3"/>
+    </row>
+    <row r="992" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A992" s="3"/>
+    </row>
+    <row r="993" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A993" s="3"/>
+    </row>
+    <row r="994" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A994" s="3"/>
+    </row>
+    <row r="995" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A995" s="3"/>
+    </row>
+    <row r="996" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A996" s="3"/>
+    </row>
+    <row r="997" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A997" s="3"/>
+    </row>
+    <row r="998" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A998" s="3"/>
+    </row>
+    <row r="999" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A999" s="3"/>
+    </row>
+    <row r="1000" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1000" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>